--- a/examples/showcase/data/Battle.xlsx
+++ b/examples/showcase/data/Battle.xlsx
@@ -52,7 +52,7 @@
     <t>@schema</t>
   </si>
   <si>
-    <t>139bd0c7b236a4cf</t>
+    <t>70fc913f3e9b878f</t>
   </si>
   <si>
     <t>#name</t>
@@ -118,7 +118,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>required;separator=,;parser=tuple</t>
+    <t>required;parser=tuple</t>
   </si>
   <si>
     <t>optional;range=1..100</t>
@@ -697,7 +697,7 @@
     <t>Character</t>
   </si>
   <si>
-    <t>d2c006329eed6eb3</t>
+    <t>996fe1623cec07ee</t>
   </si>
   <si>
     <t>rarity</t>
@@ -727,9 +727,6 @@
     <t>list&lt;ref&lt;Item.id&gt;&gt;</t>
   </si>
   <si>
-    <t>required;separator=,;prefix=[;suffix=]</t>
-  </si>
-  <si>
     <t>4001</t>
   </si>
   <si>
@@ -994,7 +991,7 @@
     <t>list</t>
   </si>
   <si>
-    <t>3c9049eb1a8a8b3e</t>
+    <t>e92c79afa1e2e40b</t>
   </si>
   <si>
     <t>character_id</t>
@@ -1015,7 +1012,7 @@
     <t>Buff</t>
   </si>
   <si>
-    <t>5664e2665d4d2fff</t>
+    <t>ab300d6757967f84</t>
   </si>
   <si>
     <t>duration</t>
@@ -1030,6 +1027,9 @@
     <t>list&lt;struct&lt;StatModifier&gt;&gt;</t>
   </si>
   <si>
+    <t>required;parser=json</t>
+  </si>
+  <si>
     <t>6001</t>
   </si>
   <si>
@@ -1213,7 +1213,7 @@
     <t>DropGroup</t>
   </si>
   <si>
-    <t>198e3bc14f1ae42b</t>
+    <t>ddc8f184c6f4ca0b</t>
   </si>
   <si>
     <t>7001</t>
@@ -1339,7 +1339,7 @@
     <t>DropEntry</t>
   </si>
   <si>
-    <t>430779b9896d046d</t>
+    <t>38e6bc608bd50c74</t>
   </si>
   <si>
     <t>group_id</t>
@@ -1438,7 +1438,7 @@
     <t>Monster</t>
   </si>
   <si>
-    <t>528a6db4e291242f</t>
+    <t>3f0a6c4362bc5a57</t>
   </si>
   <si>
     <t>level</t>
@@ -2239,7 +2239,7 @@
     <t>Stage</t>
   </si>
   <si>
-    <t>ff19dbdf0f0e4b94</t>
+    <t>bede35fc90989759</t>
   </si>
   <si>
     <t>monster_ids</t>
@@ -2740,7 +2740,7 @@
     <t>StageReward</t>
   </si>
   <si>
-    <t>88182c561a3498ab</t>
+    <t>0c97ec70735264e3</t>
   </si>
   <si>
     <t>stage_id</t>
@@ -2809,7 +2809,7 @@
     <t>Dungeon</t>
   </si>
   <si>
-    <t>eee9bc33ced1d705</t>
+    <t>b0a9bd963cf8bc87</t>
   </si>
   <si>
     <t>stage_ids</t>
@@ -4318,7 +4318,7 @@
         <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>234</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
         <v>31</v>
@@ -4643,7 +4643,7 @@
         <v>30</v>
       </c>
       <c r="G11" t="s">
-        <v>234</v>
+        <v>30</v>
       </c>
       <c r="H11" t="s">
         <v>31</v>
@@ -4656,36 +4656,36 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
+        <v>234</v>
+      </c>
+      <c r="B13" t="s">
         <v>235</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>236</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>237</v>
-      </c>
-      <c r="D13" t="s">
-        <v>238</v>
       </c>
       <c r="E13" t="s">
         <v>109</v>
       </c>
       <c r="F13" t="s">
+        <v>238</v>
+      </c>
+      <c r="G13" t="s">
         <v>239</v>
-      </c>
-      <c r="G13" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
+        <v>240</v>
+      </c>
+      <c r="B14" t="s">
         <v>241</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>242</v>
-      </c>
-      <c r="C14" t="s">
-        <v>243</v>
       </c>
       <c r="D14" t="s">
         <v>43</v>
@@ -4694,21 +4694,21 @@
         <v>115</v>
       </c>
       <c r="F14" t="s">
+        <v>243</v>
+      </c>
+      <c r="G14" t="s">
         <v>244</v>
-      </c>
-      <c r="G14" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
+        <v>245</v>
+      </c>
+      <c r="B15" t="s">
         <v>246</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>247</v>
-      </c>
-      <c r="C15" t="s">
-        <v>248</v>
       </c>
       <c r="D15" t="s">
         <v>57</v>
@@ -4717,21 +4717,21 @@
         <v>121</v>
       </c>
       <c r="F15" t="s">
+        <v>248</v>
+      </c>
+      <c r="G15" t="s">
         <v>249</v>
-      </c>
-      <c r="G15" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
+        <v>250</v>
+      </c>
+      <c r="B16" t="s">
         <v>251</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>252</v>
-      </c>
-      <c r="C16" t="s">
-        <v>253</v>
       </c>
       <c r="D16" t="s">
         <v>63</v>
@@ -4740,21 +4740,21 @@
         <v>127</v>
       </c>
       <c r="F16" t="s">
+        <v>253</v>
+      </c>
+      <c r="G16" t="s">
         <v>254</v>
-      </c>
-      <c r="G16" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
+        <v>255</v>
+      </c>
+      <c r="B17" t="s">
         <v>256</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>257</v>
-      </c>
-      <c r="C17" t="s">
-        <v>258</v>
       </c>
       <c r="D17" t="s">
         <v>69</v>
@@ -4763,21 +4763,21 @@
         <v>133</v>
       </c>
       <c r="F17" t="s">
+        <v>258</v>
+      </c>
+      <c r="G17" t="s">
         <v>259</v>
-      </c>
-      <c r="G17" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
+        <v>260</v>
+      </c>
+      <c r="B18" t="s">
         <v>261</v>
       </c>
-      <c r="B18" t="s">
-        <v>262</v>
-      </c>
       <c r="C18" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D18" t="s">
         <v>77</v>
@@ -4786,21 +4786,21 @@
         <v>139</v>
       </c>
       <c r="F18" t="s">
+        <v>262</v>
+      </c>
+      <c r="G18" t="s">
         <v>263</v>
-      </c>
-      <c r="G18" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
+        <v>264</v>
+      </c>
+      <c r="B19" t="s">
         <v>265</v>
       </c>
-      <c r="B19" t="s">
-        <v>266</v>
-      </c>
       <c r="C19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D19" t="s">
         <v>83</v>
@@ -4809,21 +4809,21 @@
         <v>145</v>
       </c>
       <c r="F19" t="s">
+        <v>266</v>
+      </c>
+      <c r="G19" t="s">
         <v>267</v>
-      </c>
-      <c r="G19" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
+        <v>268</v>
+      </c>
+      <c r="B20" t="s">
         <v>269</v>
       </c>
-      <c r="B20" t="s">
-        <v>270</v>
-      </c>
       <c r="C20" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D20" t="s">
         <v>89</v>
@@ -4832,21 +4832,21 @@
         <v>151</v>
       </c>
       <c r="F20" t="s">
+        <v>270</v>
+      </c>
+      <c r="G20" t="s">
         <v>271</v>
-      </c>
-      <c r="G20" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
+        <v>272</v>
+      </c>
+      <c r="B21" t="s">
         <v>273</v>
       </c>
-      <c r="B21" t="s">
-        <v>274</v>
-      </c>
       <c r="C21" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D21" t="s">
         <v>95</v>
@@ -4855,21 +4855,21 @@
         <v>157</v>
       </c>
       <c r="F21" t="s">
+        <v>274</v>
+      </c>
+      <c r="G21" t="s">
         <v>275</v>
-      </c>
-      <c r="G21" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
+        <v>276</v>
+      </c>
+      <c r="B22" t="s">
         <v>277</v>
       </c>
-      <c r="B22" t="s">
-        <v>278</v>
-      </c>
       <c r="C22" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D22" t="s">
         <v>101</v>
@@ -4878,21 +4878,21 @@
         <v>163</v>
       </c>
       <c r="F22" t="s">
+        <v>278</v>
+      </c>
+      <c r="G22" t="s">
         <v>279</v>
-      </c>
-      <c r="G22" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
+        <v>280</v>
+      </c>
+      <c r="B23" t="s">
         <v>281</v>
       </c>
-      <c r="B23" t="s">
-        <v>282</v>
-      </c>
       <c r="C23" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D23" t="s">
         <v>107</v>
@@ -4901,21 +4901,21 @@
         <v>169</v>
       </c>
       <c r="F23" t="s">
+        <v>282</v>
+      </c>
+      <c r="G23" t="s">
         <v>283</v>
-      </c>
-      <c r="G23" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
+        <v>284</v>
+      </c>
+      <c r="B24" t="s">
         <v>285</v>
       </c>
-      <c r="B24" t="s">
-        <v>286</v>
-      </c>
       <c r="C24" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D24" t="s">
         <v>113</v>
@@ -4924,21 +4924,21 @@
         <v>175</v>
       </c>
       <c r="F24" t="s">
+        <v>286</v>
+      </c>
+      <c r="G24" t="s">
         <v>287</v>
-      </c>
-      <c r="G24" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
+        <v>288</v>
+      </c>
+      <c r="B25" t="s">
         <v>289</v>
       </c>
-      <c r="B25" t="s">
-        <v>290</v>
-      </c>
       <c r="C25" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D25" t="s">
         <v>119</v>
@@ -4947,21 +4947,21 @@
         <v>181</v>
       </c>
       <c r="F25" t="s">
+        <v>290</v>
+      </c>
+      <c r="G25" t="s">
         <v>291</v>
-      </c>
-      <c r="G25" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
+        <v>292</v>
+      </c>
+      <c r="B26" t="s">
         <v>293</v>
       </c>
-      <c r="B26" t="s">
-        <v>294</v>
-      </c>
       <c r="C26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D26" t="s">
         <v>125</v>
@@ -4970,21 +4970,21 @@
         <v>187</v>
       </c>
       <c r="F26" t="s">
+        <v>294</v>
+      </c>
+      <c r="G26" t="s">
         <v>295</v>
-      </c>
-      <c r="G26" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
+        <v>296</v>
+      </c>
+      <c r="B27" t="s">
         <v>297</v>
       </c>
-      <c r="B27" t="s">
-        <v>298</v>
-      </c>
       <c r="C27" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D27" t="s">
         <v>131</v>
@@ -4993,21 +4993,21 @@
         <v>193</v>
       </c>
       <c r="F27" t="s">
+        <v>298</v>
+      </c>
+      <c r="G27" t="s">
         <v>299</v>
-      </c>
-      <c r="G27" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
+        <v>300</v>
+      </c>
+      <c r="B28" t="s">
         <v>301</v>
       </c>
-      <c r="B28" t="s">
-        <v>302</v>
-      </c>
       <c r="C28" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D28" t="s">
         <v>137</v>
@@ -5016,21 +5016,21 @@
         <v>199</v>
       </c>
       <c r="F28" t="s">
+        <v>302</v>
+      </c>
+      <c r="G28" t="s">
         <v>303</v>
-      </c>
-      <c r="G28" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
+        <v>304</v>
+      </c>
+      <c r="B29" t="s">
         <v>305</v>
       </c>
-      <c r="B29" t="s">
-        <v>306</v>
-      </c>
       <c r="C29" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D29" t="s">
         <v>143</v>
@@ -5039,21 +5039,21 @@
         <v>205</v>
       </c>
       <c r="F29" t="s">
+        <v>306</v>
+      </c>
+      <c r="G29" t="s">
         <v>307</v>
-      </c>
-      <c r="G29" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
+        <v>308</v>
+      </c>
+      <c r="B30" t="s">
         <v>309</v>
       </c>
-      <c r="B30" t="s">
-        <v>310</v>
-      </c>
       <c r="C30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D30" t="s">
         <v>149</v>
@@ -5062,21 +5062,21 @@
         <v>211</v>
       </c>
       <c r="F30" t="s">
+        <v>310</v>
+      </c>
+      <c r="G30" t="s">
         <v>311</v>
-      </c>
-      <c r="G30" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
+        <v>312</v>
+      </c>
+      <c r="B31" t="s">
         <v>313</v>
       </c>
-      <c r="B31" t="s">
-        <v>314</v>
-      </c>
       <c r="C31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D31" t="s">
         <v>155</v>
@@ -5085,21 +5085,21 @@
         <v>217</v>
       </c>
       <c r="F31" t="s">
+        <v>314</v>
+      </c>
+      <c r="G31" t="s">
         <v>315</v>
-      </c>
-      <c r="G31" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
+        <v>316</v>
+      </c>
+      <c r="B32" t="s">
         <v>317</v>
       </c>
-      <c r="B32" t="s">
-        <v>318</v>
-      </c>
       <c r="C32" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D32" t="s">
         <v>161</v>
@@ -5108,10 +5108,10 @@
         <v>38</v>
       </c>
       <c r="F32" t="s">
+        <v>318</v>
+      </c>
+      <c r="G32" t="s">
         <v>319</v>
-      </c>
-      <c r="G32" t="s">
-        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -5129,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5137,7 +5137,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5158,7 +5158,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5166,13 +5166,13 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
+        <v>323</v>
+      </c>
+      <c r="C7" t="s">
         <v>324</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>325</v>
-      </c>
-      <c r="D7" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -5180,13 +5180,13 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
+        <v>323</v>
+      </c>
+      <c r="C8" t="s">
         <v>324</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>325</v>
-      </c>
-      <c r="D8" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -5194,7 +5194,7 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C9" t="s">
         <v>232</v>
@@ -5238,18 +5238,18 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B13" t="s">
         <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B14" t="s">
         <v>115</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B15" t="s">
         <v>121</v>
@@ -5271,18 +5271,18 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B16" t="s">
         <v>115</v>
       </c>
       <c r="C16" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B17" t="s">
         <v>121</v>
@@ -5293,7 +5293,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B18" t="s">
         <v>127</v>
@@ -5304,18 +5304,18 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B19" t="s">
         <v>121</v>
       </c>
       <c r="C19" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B20" t="s">
         <v>127</v>
@@ -5326,7 +5326,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s">
         <v>133</v>
@@ -5337,18 +5337,18 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B22" t="s">
         <v>127</v>
       </c>
       <c r="C22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B23" t="s">
         <v>133</v>
@@ -5359,7 +5359,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s">
         <v>139</v>
@@ -5370,18 +5370,18 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B25" t="s">
         <v>133</v>
       </c>
       <c r="C25" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s">
         <v>139</v>
@@ -5392,7 +5392,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B27" t="s">
         <v>145</v>
@@ -5403,18 +5403,18 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s">
         <v>139</v>
       </c>
       <c r="C28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s">
         <v>145</v>
@@ -5425,7 +5425,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s">
         <v>151</v>
@@ -5436,18 +5436,18 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s">
         <v>145</v>
       </c>
       <c r="C31" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s">
         <v>151</v>
@@ -5458,7 +5458,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s">
         <v>157</v>
@@ -5469,18 +5469,18 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s">
         <v>151</v>
       </c>
       <c r="C34" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B35" t="s">
         <v>157</v>
@@ -5491,7 +5491,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B36" t="s">
         <v>163</v>
@@ -5502,18 +5502,18 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B37" t="s">
         <v>157</v>
       </c>
       <c r="C37" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B38" t="s">
         <v>163</v>
@@ -5524,7 +5524,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B39" t="s">
         <v>169</v>
@@ -5535,18 +5535,18 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B40" t="s">
         <v>163</v>
       </c>
       <c r="C40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B41" t="s">
         <v>169</v>
@@ -5557,7 +5557,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B42" t="s">
         <v>175</v>
@@ -5568,18 +5568,18 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B43" t="s">
         <v>169</v>
       </c>
       <c r="C43" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B44" t="s">
         <v>175</v>
@@ -5590,7 +5590,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B45" t="s">
         <v>181</v>
@@ -5601,18 +5601,18 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B46" t="s">
         <v>175</v>
       </c>
       <c r="C46" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B47" t="s">
         <v>181</v>
@@ -5623,7 +5623,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B48" t="s">
         <v>187</v>
@@ -5634,18 +5634,18 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B49" t="s">
         <v>181</v>
       </c>
       <c r="C49" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B50" t="s">
         <v>187</v>
@@ -5656,7 +5656,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B51" t="s">
         <v>193</v>
@@ -5667,18 +5667,18 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B52" t="s">
         <v>187</v>
       </c>
       <c r="C52" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B53" t="s">
         <v>193</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B54" t="s">
         <v>199</v>
@@ -5700,18 +5700,18 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B55" t="s">
         <v>193</v>
       </c>
       <c r="C55" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B56" t="s">
         <v>199</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B57" t="s">
         <v>205</v>
@@ -5733,18 +5733,18 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B58" t="s">
         <v>199</v>
       </c>
       <c r="C58" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B59" t="s">
         <v>205</v>
@@ -5755,7 +5755,7 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B60" t="s">
         <v>211</v>
@@ -5766,18 +5766,18 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B61" t="s">
         <v>205</v>
       </c>
       <c r="C61" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B62" t="s">
         <v>211</v>
@@ -5788,7 +5788,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B63" t="s">
         <v>217</v>
@@ -5799,18 +5799,18 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B64" t="s">
         <v>211</v>
       </c>
       <c r="C64" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B65" t="s">
         <v>217</v>
@@ -5821,7 +5821,7 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B66" t="s">
         <v>38</v>
@@ -5832,18 +5832,18 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B67" t="s">
         <v>217</v>
       </c>
       <c r="C67" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B68" t="s">
         <v>38</v>
@@ -5854,7 +5854,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B69" t="s">
         <v>46</v>
@@ -5865,18 +5865,18 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B70" t="s">
         <v>38</v>
       </c>
       <c r="C70" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B71" t="s">
         <v>46</v>
@@ -5887,7 +5887,7 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B72" t="s">
         <v>52</v>
@@ -5911,7 +5911,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5943,7 +5943,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5957,10 +5957,10 @@
         <v>11</v>
       </c>
       <c r="D7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E7" t="s">
         <v>331</v>
-      </c>
-      <c r="E7" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5974,10 +5974,10 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
+        <v>330</v>
+      </c>
+      <c r="E8" t="s">
         <v>331</v>
-      </c>
-      <c r="E8" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5991,10 +5991,10 @@
         <v>21</v>
       </c>
       <c r="D9" t="s">
+        <v>332</v>
+      </c>
+      <c r="E9" t="s">
         <v>333</v>
-      </c>
-      <c r="E9" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -6028,7 +6028,7 @@
         <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>234</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -6609,7 +6609,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -6690,7 +6690,7 @@
         <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -6743,7 +6743,7 @@
         <v>397</v>
       </c>
       <c r="B13" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C13" t="s">
         <v>448</v>
@@ -6760,7 +6760,7 @@
         <v>397</v>
       </c>
       <c r="B14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C14" t="s">
         <v>449</v>
@@ -6794,7 +6794,7 @@
         <v>399</v>
       </c>
       <c r="B16" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C16" t="s">
         <v>449</v>
@@ -6811,7 +6811,7 @@
         <v>399</v>
       </c>
       <c r="B17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C17" t="s">
         <v>450</v>
@@ -6845,7 +6845,7 @@
         <v>401</v>
       </c>
       <c r="B19" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C19" t="s">
         <v>450</v>
@@ -6862,7 +6862,7 @@
         <v>401</v>
       </c>
       <c r="B20" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C20" t="s">
         <v>451</v>
@@ -6896,7 +6896,7 @@
         <v>403</v>
       </c>
       <c r="B22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C22" t="s">
         <v>451</v>
@@ -6913,7 +6913,7 @@
         <v>403</v>
       </c>
       <c r="B23" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C23" t="s">
         <v>452</v>
@@ -6947,7 +6947,7 @@
         <v>405</v>
       </c>
       <c r="B25" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C25" t="s">
         <v>452</v>
@@ -6964,7 +6964,7 @@
         <v>405</v>
       </c>
       <c r="B26" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C26" t="s">
         <v>453</v>
@@ -6998,7 +6998,7 @@
         <v>407</v>
       </c>
       <c r="B28" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C28" t="s">
         <v>453</v>
@@ -7015,7 +7015,7 @@
         <v>407</v>
       </c>
       <c r="B29" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C29" t="s">
         <v>454</v>
@@ -7049,7 +7049,7 @@
         <v>409</v>
       </c>
       <c r="B31" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C31" t="s">
         <v>454</v>
@@ -7066,7 +7066,7 @@
         <v>409</v>
       </c>
       <c r="B32" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C32" t="s">
         <v>455</v>
@@ -7100,7 +7100,7 @@
         <v>411</v>
       </c>
       <c r="B34" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C34" t="s">
         <v>455</v>
@@ -7117,7 +7117,7 @@
         <v>411</v>
       </c>
       <c r="B35" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C35" t="s">
         <v>456</v>
@@ -7151,7 +7151,7 @@
         <v>413</v>
       </c>
       <c r="B37" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C37" t="s">
         <v>456</v>
@@ -7168,7 +7168,7 @@
         <v>413</v>
       </c>
       <c r="B38" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C38" t="s">
         <v>457</v>
@@ -7202,7 +7202,7 @@
         <v>415</v>
       </c>
       <c r="B40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C40" t="s">
         <v>457</v>
@@ -7219,7 +7219,7 @@
         <v>415</v>
       </c>
       <c r="B41" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C41" t="s">
         <v>458</v>
@@ -7253,7 +7253,7 @@
         <v>417</v>
       </c>
       <c r="B43" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C43" t="s">
         <v>458</v>
@@ -7270,7 +7270,7 @@
         <v>417</v>
       </c>
       <c r="B44" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C44" t="s">
         <v>459</v>
@@ -7304,7 +7304,7 @@
         <v>419</v>
       </c>
       <c r="B46" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C46" t="s">
         <v>459</v>
@@ -7321,7 +7321,7 @@
         <v>419</v>
       </c>
       <c r="B47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C47" t="s">
         <v>460</v>
@@ -7355,7 +7355,7 @@
         <v>421</v>
       </c>
       <c r="B49" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C49" t="s">
         <v>460</v>
@@ -7372,7 +7372,7 @@
         <v>421</v>
       </c>
       <c r="B50" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C50" t="s">
         <v>461</v>
@@ -7406,7 +7406,7 @@
         <v>423</v>
       </c>
       <c r="B52" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C52" t="s">
         <v>461</v>
@@ -7423,7 +7423,7 @@
         <v>423</v>
       </c>
       <c r="B53" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C53" t="s">
         <v>462</v>
@@ -7457,7 +7457,7 @@
         <v>425</v>
       </c>
       <c r="B55" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C55" t="s">
         <v>462</v>
@@ -7474,7 +7474,7 @@
         <v>425</v>
       </c>
       <c r="B56" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C56" t="s">
         <v>463</v>
@@ -7508,7 +7508,7 @@
         <v>427</v>
       </c>
       <c r="B58" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C58" t="s">
         <v>463</v>
@@ -7525,7 +7525,7 @@
         <v>427</v>
       </c>
       <c r="B59" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C59" t="s">
         <v>464</v>
@@ -7559,7 +7559,7 @@
         <v>429</v>
       </c>
       <c r="B61" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C61" t="s">
         <v>464</v>
@@ -7576,7 +7576,7 @@
         <v>429</v>
       </c>
       <c r="B62" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C62" t="s">
         <v>465</v>
@@ -7610,7 +7610,7 @@
         <v>431</v>
       </c>
       <c r="B64" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C64" t="s">
         <v>465</v>
@@ -7627,7 +7627,7 @@
         <v>431</v>
       </c>
       <c r="B65" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C65" t="s">
         <v>466</v>
@@ -7661,7 +7661,7 @@
         <v>433</v>
       </c>
       <c r="B67" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C67" t="s">
         <v>466</v>
@@ -7678,7 +7678,7 @@
         <v>433</v>
       </c>
       <c r="B68" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C68" t="s">
         <v>467</v>
@@ -7712,7 +7712,7 @@
         <v>435</v>
       </c>
       <c r="B70" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C70" t="s">
         <v>467</v>
@@ -7729,7 +7729,7 @@
         <v>435</v>
       </c>
       <c r="B71" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C71" t="s">
         <v>468</v>
@@ -7936,7 +7936,7 @@
         <v>475</v>
       </c>
       <c r="C13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D13" t="s">
         <v>48</v>
@@ -8725,7 +8725,7 @@
         <v>397</v>
       </c>
       <c r="F52" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -8745,7 +8745,7 @@
         <v>399</v>
       </c>
       <c r="F53" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -8765,7 +8765,7 @@
         <v>401</v>
       </c>
       <c r="F54" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -8785,7 +8785,7 @@
         <v>403</v>
       </c>
       <c r="F55" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -8805,7 +8805,7 @@
         <v>405</v>
       </c>
       <c r="F56" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -8825,7 +8825,7 @@
         <v>407</v>
       </c>
       <c r="F57" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -9516,7 +9516,7 @@
         <v>736</v>
       </c>
       <c r="C92" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D92" t="s">
         <v>40</v>
@@ -9669,7 +9669,7 @@
         <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>234</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
         <v>30</v>
@@ -10266,7 +10266,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -10385,7 +10385,7 @@
         <v>744</v>
       </c>
       <c r="B13" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C13" t="s">
         <v>908</v>
@@ -10399,7 +10399,7 @@
         <v>744</v>
       </c>
       <c r="B14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C14" t="s">
         <v>909</v>
@@ -10413,7 +10413,7 @@
         <v>748</v>
       </c>
       <c r="B15" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C15" t="s">
         <v>909</v>
@@ -10427,7 +10427,7 @@
         <v>748</v>
       </c>
       <c r="B16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C16" t="s">
         <v>910</v>
@@ -10441,7 +10441,7 @@
         <v>752</v>
       </c>
       <c r="B17" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C17" t="s">
         <v>910</v>
@@ -10455,7 +10455,7 @@
         <v>752</v>
       </c>
       <c r="B18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C18" t="s">
         <v>911</v>
@@ -10469,7 +10469,7 @@
         <v>756</v>
       </c>
       <c r="B19" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C19" t="s">
         <v>911</v>
@@ -10483,7 +10483,7 @@
         <v>756</v>
       </c>
       <c r="B20" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C20" t="s">
         <v>912</v>
@@ -10497,7 +10497,7 @@
         <v>760</v>
       </c>
       <c r="B21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C21" t="s">
         <v>912</v>
@@ -10511,7 +10511,7 @@
         <v>760</v>
       </c>
       <c r="B22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C22" t="s">
         <v>913</v>
@@ -10525,7 +10525,7 @@
         <v>764</v>
       </c>
       <c r="B23" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C23" t="s">
         <v>913</v>
@@ -10539,7 +10539,7 @@
         <v>764</v>
       </c>
       <c r="B24" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C24" t="s">
         <v>448</v>
@@ -10553,7 +10553,7 @@
         <v>768</v>
       </c>
       <c r="B25" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C25" t="s">
         <v>448</v>
@@ -10567,7 +10567,7 @@
         <v>768</v>
       </c>
       <c r="B26" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C26" t="s">
         <v>449</v>
@@ -10581,7 +10581,7 @@
         <v>772</v>
       </c>
       <c r="B27" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C27" t="s">
         <v>449</v>
@@ -10595,7 +10595,7 @@
         <v>772</v>
       </c>
       <c r="B28" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C28" t="s">
         <v>450</v>
@@ -10609,7 +10609,7 @@
         <v>776</v>
       </c>
       <c r="B29" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C29" t="s">
         <v>450</v>
@@ -10623,7 +10623,7 @@
         <v>776</v>
       </c>
       <c r="B30" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C30" t="s">
         <v>451</v>
@@ -10637,7 +10637,7 @@
         <v>780</v>
       </c>
       <c r="B31" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C31" t="s">
         <v>451</v>
@@ -10651,7 +10651,7 @@
         <v>780</v>
       </c>
       <c r="B32" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C32" t="s">
         <v>452</v>
@@ -10665,7 +10665,7 @@
         <v>784</v>
       </c>
       <c r="B33" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C33" t="s">
         <v>452</v>
@@ -10679,7 +10679,7 @@
         <v>784</v>
       </c>
       <c r="B34" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C34" t="s">
         <v>453</v>
@@ -10693,7 +10693,7 @@
         <v>788</v>
       </c>
       <c r="B35" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C35" t="s">
         <v>453</v>
@@ -10707,7 +10707,7 @@
         <v>788</v>
       </c>
       <c r="B36" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C36" t="s">
         <v>454</v>
@@ -10721,7 +10721,7 @@
         <v>792</v>
       </c>
       <c r="B37" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C37" t="s">
         <v>454</v>
@@ -10735,7 +10735,7 @@
         <v>792</v>
       </c>
       <c r="B38" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C38" t="s">
         <v>455</v>
@@ -10749,7 +10749,7 @@
         <v>796</v>
       </c>
       <c r="B39" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C39" t="s">
         <v>455</v>
@@ -10763,7 +10763,7 @@
         <v>796</v>
       </c>
       <c r="B40" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C40" t="s">
         <v>456</v>
@@ -10777,7 +10777,7 @@
         <v>800</v>
       </c>
       <c r="B41" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C41" t="s">
         <v>456</v>
@@ -10791,7 +10791,7 @@
         <v>800</v>
       </c>
       <c r="B42" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C42" t="s">
         <v>457</v>
@@ -10805,7 +10805,7 @@
         <v>804</v>
       </c>
       <c r="B43" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C43" t="s">
         <v>457</v>
@@ -10819,7 +10819,7 @@
         <v>804</v>
       </c>
       <c r="B44" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C44" t="s">
         <v>458</v>
@@ -10833,7 +10833,7 @@
         <v>808</v>
       </c>
       <c r="B45" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C45" t="s">
         <v>458</v>
@@ -10847,7 +10847,7 @@
         <v>808</v>
       </c>
       <c r="B46" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C46" t="s">
         <v>459</v>
@@ -10861,7 +10861,7 @@
         <v>812</v>
       </c>
       <c r="B47" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C47" t="s">
         <v>459</v>
@@ -10875,7 +10875,7 @@
         <v>812</v>
       </c>
       <c r="B48" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C48" t="s">
         <v>460</v>
@@ -10889,7 +10889,7 @@
         <v>816</v>
       </c>
       <c r="B49" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C49" t="s">
         <v>460</v>
@@ -10903,7 +10903,7 @@
         <v>816</v>
       </c>
       <c r="B50" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C50" t="s">
         <v>461</v>
@@ -10917,7 +10917,7 @@
         <v>820</v>
       </c>
       <c r="B51" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C51" t="s">
         <v>461</v>
@@ -10931,7 +10931,7 @@
         <v>820</v>
       </c>
       <c r="B52" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C52" t="s">
         <v>462</v>
@@ -10945,7 +10945,7 @@
         <v>824</v>
       </c>
       <c r="B53" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C53" t="s">
         <v>462</v>
@@ -10959,7 +10959,7 @@
         <v>824</v>
       </c>
       <c r="B54" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C54" t="s">
         <v>463</v>
@@ -10973,7 +10973,7 @@
         <v>828</v>
       </c>
       <c r="B55" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C55" t="s">
         <v>463</v>
@@ -10987,7 +10987,7 @@
         <v>828</v>
       </c>
       <c r="B56" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C56" t="s">
         <v>464</v>
@@ -11001,7 +11001,7 @@
         <v>832</v>
       </c>
       <c r="B57" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C57" t="s">
         <v>464</v>
@@ -11015,7 +11015,7 @@
         <v>832</v>
       </c>
       <c r="B58" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C58" t="s">
         <v>465</v>
@@ -11029,7 +11029,7 @@
         <v>836</v>
       </c>
       <c r="B59" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C59" t="s">
         <v>465</v>
@@ -11043,7 +11043,7 @@
         <v>836</v>
       </c>
       <c r="B60" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C60" t="s">
         <v>466</v>
@@ -11057,7 +11057,7 @@
         <v>840</v>
       </c>
       <c r="B61" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C61" t="s">
         <v>466</v>
@@ -11071,7 +11071,7 @@
         <v>840</v>
       </c>
       <c r="B62" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C62" t="s">
         <v>467</v>
@@ -11085,7 +11085,7 @@
         <v>844</v>
       </c>
       <c r="B63" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C63" t="s">
         <v>467</v>
@@ -11099,7 +11099,7 @@
         <v>844</v>
       </c>
       <c r="B64" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C64" t="s">
         <v>468</v>
@@ -11113,7 +11113,7 @@
         <v>848</v>
       </c>
       <c r="B65" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C65" t="s">
         <v>468</v>
@@ -11127,7 +11127,7 @@
         <v>848</v>
       </c>
       <c r="B66" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C66" t="s">
         <v>469</v>
@@ -11141,7 +11141,7 @@
         <v>852</v>
       </c>
       <c r="B67" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C67" t="s">
         <v>469</v>
@@ -11155,7 +11155,7 @@
         <v>852</v>
       </c>
       <c r="B68" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C68" t="s">
         <v>914</v>
@@ -11169,7 +11169,7 @@
         <v>856</v>
       </c>
       <c r="B69" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C69" t="s">
         <v>914</v>
@@ -11183,7 +11183,7 @@
         <v>856</v>
       </c>
       <c r="B70" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C70" t="s">
         <v>915</v>
@@ -11197,7 +11197,7 @@
         <v>860</v>
       </c>
       <c r="B71" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C71" t="s">
         <v>915</v>
@@ -11211,7 +11211,7 @@
         <v>860</v>
       </c>
       <c r="B72" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C72" t="s">
         <v>916</v>
@@ -11225,7 +11225,7 @@
         <v>864</v>
       </c>
       <c r="B73" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C73" t="s">
         <v>916</v>
@@ -11239,7 +11239,7 @@
         <v>864</v>
       </c>
       <c r="B74" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C74" t="s">
         <v>917</v>
@@ -11253,7 +11253,7 @@
         <v>868</v>
       </c>
       <c r="B75" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C75" t="s">
         <v>917</v>
@@ -11267,7 +11267,7 @@
         <v>868</v>
       </c>
       <c r="B76" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C76" t="s">
         <v>918</v>
@@ -11281,7 +11281,7 @@
         <v>872</v>
       </c>
       <c r="B77" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C77" t="s">
         <v>918</v>
@@ -11295,7 +11295,7 @@
         <v>872</v>
       </c>
       <c r="B78" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C78" t="s">
         <v>919</v>
@@ -11309,7 +11309,7 @@
         <v>876</v>
       </c>
       <c r="B79" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C79" t="s">
         <v>919</v>
@@ -11323,7 +11323,7 @@
         <v>876</v>
       </c>
       <c r="B80" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C80" t="s">
         <v>920</v>
@@ -11337,7 +11337,7 @@
         <v>880</v>
       </c>
       <c r="B81" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C81" t="s">
         <v>920</v>
@@ -11351,7 +11351,7 @@
         <v>880</v>
       </c>
       <c r="B82" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C82" t="s">
         <v>921</v>
@@ -11365,7 +11365,7 @@
         <v>884</v>
       </c>
       <c r="B83" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C83" t="s">
         <v>921</v>
@@ -11379,7 +11379,7 @@
         <v>884</v>
       </c>
       <c r="B84" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C84" t="s">
         <v>922</v>
@@ -11393,7 +11393,7 @@
         <v>888</v>
       </c>
       <c r="B85" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C85" t="s">
         <v>922</v>
@@ -11407,7 +11407,7 @@
         <v>888</v>
       </c>
       <c r="B86" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C86" t="s">
         <v>923</v>
@@ -11421,7 +11421,7 @@
         <v>892</v>
       </c>
       <c r="B87" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C87" t="s">
         <v>923</v>
@@ -11435,7 +11435,7 @@
         <v>892</v>
       </c>
       <c r="B88" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C88" t="s">
         <v>924</v>
@@ -11449,7 +11449,7 @@
         <v>896</v>
       </c>
       <c r="B89" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C89" t="s">
         <v>924</v>
@@ -11463,7 +11463,7 @@
         <v>896</v>
       </c>
       <c r="B90" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C90" t="s">
         <v>925</v>
@@ -11477,7 +11477,7 @@
         <v>900</v>
       </c>
       <c r="B91" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C91" t="s">
         <v>925</v>
@@ -11491,7 +11491,7 @@
         <v>900</v>
       </c>
       <c r="B92" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C92" t="s">
         <v>926</v>

--- a/examples/showcase/data/Battle.xlsx
+++ b/examples/showcase/data/Battle.xlsx
@@ -3820,740 +3820,740 @@
       <c r="I12" s="6"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="5"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="5"/>
+      <c r="I14" s="5" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="5"/>
+      <c r="I15" s="5" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="F16" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="5"/>
+      <c r="I16" s="5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="2:9">
+      <c r="B17" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="I17" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="2:9">
+      <c r="B18" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="5"/>
+      <c r="I18" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="2:9">
+      <c r="B19" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="5"/>
+      <c r="I19" s="5" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="2:9">
+      <c r="B20" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="H20" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="I20" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="2:9">
+      <c r="B21" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="F21" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="5"/>
+      <c r="I21" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="2:9">
+      <c r="B22" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="F22" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="G22" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="5"/>
+      <c r="I22" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="2:9">
+      <c r="B23" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="F23" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="I23" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="2:9">
+      <c r="B24" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="G24" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="5"/>
+      <c r="I24" s="5" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="2:9">
+      <c r="B25" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="5"/>
+      <c r="I25" s="5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="2:9">
+      <c r="B26" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="F26" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="H26" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="I26" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="2:9">
+      <c r="B27" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="5"/>
+      <c r="I27" s="5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="2:9">
+      <c r="B28" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="F28" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="G28" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="5"/>
+      <c r="I28" s="5" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="2:9">
+      <c r="B29" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="F29" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="H29" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="I29" s="5" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="2:9">
+      <c r="B30" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="E30" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="F30" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="G30" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="5"/>
+      <c r="I30" s="5" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="2:9">
+      <c r="B31" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="F31" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5" t="s">
+      <c r="H31" s="5"/>
+      <c r="I31" s="5" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="2:9">
+      <c r="B32" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="E32" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="F32" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="G32" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="H32" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H32" s="5" t="s">
+      <c r="I32" s="5" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="5" t="s">
+    <row r="33" spans="2:9">
+      <c r="B33" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="D33" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="E33" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="F33" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="G33" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5" t="s">
+      <c r="H33" s="5"/>
+      <c r="I33" s="5" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="2:9">
+      <c r="B34" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="E34" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="F34" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="G34" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5" t="s">
+      <c r="H34" s="5"/>
+      <c r="I34" s="5" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="5" t="s">
+    <row r="35" spans="2:9">
+      <c r="B35" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="F35" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="G35" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="H35" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="I35" s="5" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="5" t="s">
+    <row r="36" spans="2:9">
+      <c r="B36" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="E36" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="F36" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="G36" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5" t="s">
+      <c r="H36" s="5"/>
+      <c r="I36" s="5" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="5" t="s">
+    <row r="37" spans="2:9">
+      <c r="B37" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="C37" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="D37" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="E37" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="F37" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="G37" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5" t="s">
+      <c r="H37" s="5"/>
+      <c r="I37" s="5" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="5" t="s">
+    <row r="38" spans="2:9">
+      <c r="B38" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="C38" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="E38" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="F38" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="G38" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="H38" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="I38" s="5" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="5" t="s">
+    <row r="39" spans="2:9">
+      <c r="B39" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="C39" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="E39" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="F39" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="G39" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5" t="s">
+      <c r="H39" s="5"/>
+      <c r="I39" s="5" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="5" t="s">
+    <row r="40" spans="2:9">
+      <c r="B40" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="C40" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="D40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="E40" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="F40" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="G40" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5" t="s">
+      <c r="H40" s="5"/>
+      <c r="I40" s="5" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
-      <c r="A41" s="5" t="s">
+    <row r="41" spans="2:9">
+      <c r="B41" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="C41" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="E41" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="F41" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="G41" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="H41" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="I41" s="5" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="5" t="s">
+    <row r="42" spans="2:9">
+      <c r="B42" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="D42" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="E42" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="F42" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="G42" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5" t="s">
+      <c r="H42" s="5"/>
+      <c r="I42" s="5" t="s">
         <v>222</v>
       </c>
     </row>
@@ -4719,142 +4719,142 @@
       <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>932</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>933</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>934</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>935</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>936</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>937</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>938</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>939</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>940</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>941</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>942</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>943</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>944</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>945</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>946</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>947</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="2:5">
+      <c r="B17" s="5" t="s">
         <v>948</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>949</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>950</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="2:5">
+      <c r="B18" s="5" t="s">
         <v>952</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>954</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="2:5">
+      <c r="B19" s="5" t="s">
         <v>956</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>957</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>958</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>959</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="2:5">
+      <c r="B20" s="5" t="s">
         <v>960</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>961</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>962</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>963</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="2:5">
+      <c r="B21" s="5" t="s">
         <v>964</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>965</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>966</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="2:5">
+      <c r="B22" s="5" t="s">
         <v>968</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>969</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>970</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>971</v>
       </c>
     </row>
@@ -5061,462 +5061,462 @@
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="H14" s="5" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="H15" s="5" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="F16" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="H16" s="5" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="2:8">
+      <c r="B17" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="2:8">
+      <c r="B18" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="H18" s="5" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="2:8">
+      <c r="B19" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="2:8">
+      <c r="B20" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="H20" s="5" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="2:8">
+      <c r="B21" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="F21" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="H21" s="5" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="2:8">
+      <c r="B22" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="F22" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="G22" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="H22" s="5" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="2:8">
+      <c r="B23" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="F23" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="2:8">
+      <c r="B24" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="G24" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="H24" s="5" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="2:8">
+      <c r="B25" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="H25" s="5" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="2:8">
+      <c r="B26" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="F26" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="H26" s="5" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="2:8">
+      <c r="B27" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="2:8">
+      <c r="B28" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>301</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="F28" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="G28" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="H28" s="5" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="2:8">
+      <c r="B29" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="F29" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="H29" s="5" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="2:8">
+      <c r="B30" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="E30" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="F30" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="G30" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="H30" s="5" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="2:8">
+      <c r="B31" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="F31" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="H31" s="5" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="2:8">
+      <c r="B32" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="E32" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="F32" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="G32" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="H32" s="5" t="s">
         <v>319</v>
       </c>
     </row>
@@ -5660,662 +5660,662 @@
       <c r="D12" s="6"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="2:4">
+      <c r="B17" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="2:4">
+      <c r="B18" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="2:4">
+      <c r="B19" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="2:4">
+      <c r="B20" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="2:4">
+      <c r="B21" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="2:4">
+      <c r="B22" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="2:4">
+      <c r="B23" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="2:4">
+      <c r="B24" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="2:4">
+      <c r="B25" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="2:4">
+      <c r="B26" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="2:4">
+      <c r="B27" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="2:4">
+      <c r="B28" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="2:4">
+      <c r="B29" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="2:4">
+      <c r="B30" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="2:4">
+      <c r="B31" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="2:4">
+      <c r="B32" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="5" t="s">
+    <row r="33" spans="2:4">
+      <c r="B33" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="D33" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="2:4">
+      <c r="B34" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="5" t="s">
+    <row r="35" spans="2:4">
+      <c r="B35" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="5" t="s">
+    <row r="36" spans="2:4">
+      <c r="B36" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="5" t="s">
+    <row r="37" spans="2:4">
+      <c r="B37" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="C37" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="D37" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="5" t="s">
+    <row r="38" spans="2:4">
+      <c r="B38" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="C38" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="5" t="s">
+    <row r="39" spans="2:4">
+      <c r="B39" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="C39" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="5" t="s">
+    <row r="40" spans="2:4">
+      <c r="B40" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="C40" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="D40" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="5" t="s">
+    <row r="41" spans="2:4">
+      <c r="B41" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="C41" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="5" t="s">
+    <row r="42" spans="2:4">
+      <c r="B42" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="D42" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="5" t="s">
+    <row r="43" spans="2:4">
+      <c r="B43" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="D43" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="5" t="s">
+    <row r="44" spans="2:4">
+      <c r="B44" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="C44" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="D44" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="5" t="s">
+    <row r="45" spans="2:4">
+      <c r="B45" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="C45" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="D45" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="5" t="s">
+    <row r="46" spans="2:4">
+      <c r="B46" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="D46" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="5" t="s">
+    <row r="47" spans="2:4">
+      <c r="B47" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="C47" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="D47" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="5" t="s">
+    <row r="48" spans="2:4">
+      <c r="B48" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="C48" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="D48" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="5" t="s">
+    <row r="49" spans="2:4">
+      <c r="B49" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="C49" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="D49" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="5" t="s">
+    <row r="50" spans="2:4">
+      <c r="B50" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="C50" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="D50" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="5" t="s">
+    <row r="51" spans="2:4">
+      <c r="B51" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="C51" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="D51" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="5" t="s">
+    <row r="52" spans="2:4">
+      <c r="B52" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="C52" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="D52" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="5" t="s">
+    <row r="53" spans="2:4">
+      <c r="B53" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="C53" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="D53" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="5" t="s">
+    <row r="54" spans="2:4">
+      <c r="B54" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="C54" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="D54" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="5" t="s">
+    <row r="55" spans="2:4">
+      <c r="B55" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="C55" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="D55" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="5" t="s">
+    <row r="56" spans="2:4">
+      <c r="B56" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="C56" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="D56" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="5" t="s">
+    <row r="57" spans="2:4">
+      <c r="B57" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="C57" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="D57" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="5" t="s">
+    <row r="58" spans="2:4">
+      <c r="B58" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="C58" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="5" t="s">
+    <row r="59" spans="2:4">
+      <c r="B59" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="C59" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="D59" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="5" t="s">
+    <row r="60" spans="2:4">
+      <c r="B60" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="C60" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="D60" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="5" t="s">
+    <row r="61" spans="2:4">
+      <c r="B61" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="C61" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="D61" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="5" t="s">
+    <row r="62" spans="2:4">
+      <c r="B62" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="C62" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="D62" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="5" t="s">
+    <row r="63" spans="2:4">
+      <c r="B63" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="C63" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="D63" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="5" t="s">
+    <row r="64" spans="2:4">
+      <c r="B64" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="C64" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="D64" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="5" t="s">
+    <row r="65" spans="2:4">
+      <c r="B65" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="C65" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="D65" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="5" t="s">
+    <row r="66" spans="2:4">
+      <c r="B66" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="C66" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="D66" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="5" t="s">
+    <row r="67" spans="2:4">
+      <c r="B67" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="C67" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="D67" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="5" t="s">
+    <row r="68" spans="2:4">
+      <c r="B68" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="C68" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="D68" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="5" t="s">
+    <row r="69" spans="2:4">
+      <c r="B69" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="C69" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="D69" s="5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="5" t="s">
+    <row r="70" spans="2:4">
+      <c r="B70" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="C70" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="D70" s="5" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="5" t="s">
+    <row r="71" spans="2:4">
+      <c r="B71" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="C71" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="D71" s="5" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="5" t="s">
+    <row r="72" spans="2:4">
+      <c r="B72" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="C72" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="D72" s="5" t="s">
         <v>161</v>
       </c>
     </row>
@@ -6470,282 +6470,282 @@
       <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="2:5">
+      <c r="B17" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="2:5">
+      <c r="B18" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="2:5">
+      <c r="B19" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="2:5">
+      <c r="B20" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="2:5">
+      <c r="B21" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="2:5">
+      <c r="B22" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="2:5">
+      <c r="B23" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="2:5">
+      <c r="B24" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="2:5">
+      <c r="B25" s="5" t="s">
         <v>371</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="2:5">
+      <c r="B26" s="5" t="s">
         <v>374</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="2:5">
+      <c r="B27" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="2:5">
+      <c r="B28" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="5" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="2:5">
+      <c r="B29" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="2:5">
+      <c r="B30" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="E30" s="5" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="2:5">
+      <c r="B31" s="5" t="s">
         <v>389</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>390</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="2:5">
+      <c r="B32" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>393</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="E32" s="5" t="s">
         <v>394</v>
       </c>
     </row>
@@ -6867,162 +6867,162 @@
       <c r="C12" s="6"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="2:3">
+      <c r="B17" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="2:3">
+      <c r="B18" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="2:3">
+      <c r="B19" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="2:3">
+      <c r="B20" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="2:3">
+      <c r="B21" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="2:3">
+      <c r="B22" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="2:3">
+      <c r="B23" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="2:3">
+      <c r="B24" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="2:3">
+      <c r="B25" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="2:3">
+      <c r="B26" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="2:3">
+      <c r="B27" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="2:3">
+      <c r="B28" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="2:3">
+      <c r="B29" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="5" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="2:3">
+      <c r="B30" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="2:3">
+      <c r="B31" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="2:3">
+      <c r="B32" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>436</v>
       </c>
     </row>
@@ -7191,1022 +7191,1022 @@
       <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="F16" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="2:6">
+      <c r="B17" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="2:6">
+      <c r="B18" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="2:6">
+      <c r="B19" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="2:6">
+      <c r="B20" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="2:6">
+      <c r="B21" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="F21" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="2:6">
+      <c r="B22" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="F22" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="2:6">
+      <c r="B23" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="F23" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="2:6">
+      <c r="B24" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="2:6">
+      <c r="B25" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="2:6">
+      <c r="B26" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="F26" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="2:6">
+      <c r="B27" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="2:6">
+      <c r="B28" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="F28" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="2:6">
+      <c r="B29" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="F29" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="2:6">
+      <c r="B30" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="E30" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="F30" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="2:6">
+      <c r="B31" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="F31" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="2:6">
+      <c r="B32" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="E32" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="F32" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+    <row r="33" spans="2:6">
+      <c r="B33" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="D33" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="E33" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="F33" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="2:6">
+      <c r="B34" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="E34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="F34" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+    <row r="35" spans="2:6">
+      <c r="B35" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="F35" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="E36" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="F36" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+    <row r="37" spans="2:6">
+      <c r="B37" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="C37" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="D37" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="E37" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="F37" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+    <row r="38" spans="2:6">
+      <c r="B38" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="C38" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="E38" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="F38" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+    <row r="39" spans="2:6">
+      <c r="B39" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="C39" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="E39" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="F39" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+    <row r="40" spans="2:6">
+      <c r="B40" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="C40" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="D40" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="E40" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="F40" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+    <row r="41" spans="2:6">
+      <c r="B41" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="C41" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="E41" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="F41" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+    <row r="42" spans="2:6">
+      <c r="B42" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="D42" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="E42" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="F42" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+    <row r="43" spans="2:6">
+      <c r="B43" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="D43" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="E43" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="F43" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+    <row r="44" spans="2:6">
+      <c r="B44" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="C44" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="D44" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="E44" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="F44" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
+    <row r="45" spans="2:6">
+      <c r="B45" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="C45" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="D45" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="E45" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="F45" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
+    <row r="46" spans="2:6">
+      <c r="B46" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="D46" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="E46" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="F46" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
+    <row r="47" spans="2:6">
+      <c r="B47" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="C47" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="D47" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="E47" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="F47" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
+    <row r="48" spans="2:6">
+      <c r="B48" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="C48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="D48" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="E48" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="F48" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
+    <row r="49" spans="2:6">
+      <c r="B49" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="C49" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="D49" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="E49" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="F49" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
+    <row r="50" spans="2:6">
+      <c r="B50" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="C50" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="D50" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="E50" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="F50" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
+    <row r="51" spans="2:6">
+      <c r="B51" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="C51" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="D51" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="E51" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="F51" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
+    <row r="52" spans="2:6">
+      <c r="B52" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="C52" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="D52" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="E52" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="F52" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
+    <row r="53" spans="2:6">
+      <c r="B53" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="C53" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="D53" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="E53" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="F53" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
+    <row r="54" spans="2:6">
+      <c r="B54" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="C54" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="D54" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="E54" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="F54" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
+    <row r="55" spans="2:6">
+      <c r="B55" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="C55" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="D55" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="E55" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="F55" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
+    <row r="56" spans="2:6">
+      <c r="B56" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="C56" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="D56" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="E56" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="F56" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
+    <row r="57" spans="2:6">
+      <c r="B57" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="C57" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="D57" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="E57" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="F57" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="C58" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="E58" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="F58" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
+    <row r="59" spans="2:6">
+      <c r="B59" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="C59" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="D59" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="E59" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="F59" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
+    <row r="60" spans="2:6">
+      <c r="B60" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="C60" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="D60" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="E60" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="F60" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="C61" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="D61" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="E61" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="F61" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
+    <row r="62" spans="2:6">
+      <c r="B62" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="C62" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="D62" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="E62" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="F62" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
+    <row r="63" spans="2:6">
+      <c r="B63" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="C63" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="D63" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="E63" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="F63" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
+    <row r="64" spans="2:6">
+      <c r="B64" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="C64" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="D64" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="E64" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="F64" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
+    <row r="65" spans="2:6">
+      <c r="B65" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="C65" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="D65" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="E65" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="F65" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
+    <row r="66" spans="2:6">
+      <c r="B66" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="C66" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="D66" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="E66" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="F66" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
+    <row r="67" spans="2:6">
+      <c r="B67" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="C67" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="D67" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="E67" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="F67" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
+    <row r="68" spans="2:6">
+      <c r="B68" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="C68" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="D68" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="D68" s="5" t="s">
+      <c r="E68" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E68" s="5" t="s">
+      <c r="F68" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
+    <row r="69" spans="2:6">
+      <c r="B69" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="C69" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="D69" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="E69" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="F69" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
+    <row r="70" spans="2:6">
+      <c r="B70" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="C70" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="D70" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="D70" s="5" t="s">
+      <c r="E70" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E70" s="5" t="s">
+      <c r="F70" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
+    <row r="71" spans="2:6">
+      <c r="B71" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="C71" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="D71" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D71" s="5" t="s">
+      <c r="E71" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="F71" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
+    <row r="72" spans="2:6">
+      <c r="B72" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="C72" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="D72" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="D72" s="5" t="s">
+      <c r="E72" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="F72" s="5" t="s">
         <v>185</v>
       </c>
     </row>
@@ -8401,1602 +8401,1602 @@
       <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>477</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>481</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="F16" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="2:7">
+      <c r="B17" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="2:7">
+      <c r="B18" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="2:7">
+      <c r="B19" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="2:7">
+      <c r="B20" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="2:7">
+      <c r="B21" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>499</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="F21" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="2:7">
+      <c r="B22" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="F22" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="G22" s="5" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="2:7">
+      <c r="B23" s="5" t="s">
         <v>504</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>505</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="F23" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="2:7">
+      <c r="B24" s="5" t="s">
         <v>507</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="G24" s="5" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="2:7">
+      <c r="B25" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="5" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="2:7">
+      <c r="B26" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="F26" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="5" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="2:7">
+      <c r="B27" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>517</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="2:7">
+      <c r="B28" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="F28" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="G28" s="5" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="2:7">
+      <c r="B29" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="F29" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="2:7">
+      <c r="B30" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="E30" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="F30" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="G30" s="5" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="2:7">
+      <c r="B31" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="F31" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="5" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="2:7">
+      <c r="B32" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="E32" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="F32" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="G32" s="5" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="5" t="s">
+    <row r="33" spans="2:7">
+      <c r="B33" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="D33" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="E33" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="F33" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="G33" s="5" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="2:7">
+      <c r="B34" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="E34" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="F34" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="G34" s="5" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="5" t="s">
+    <row r="35" spans="2:7">
+      <c r="B35" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="F35" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="G35" s="5" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="5" t="s">
+    <row r="36" spans="2:7">
+      <c r="B36" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>544</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="E36" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="F36" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="G36" s="5" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="5" t="s">
+    <row r="37" spans="2:7">
+      <c r="B37" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="C37" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="D37" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="E37" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="F37" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="G37" s="5" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="5" t="s">
+    <row r="38" spans="2:7">
+      <c r="B38" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="C38" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="E38" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="F38" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="G38" s="5" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="5" t="s">
+    <row r="39" spans="2:7">
+      <c r="B39" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="C39" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="E39" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="F39" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="G39" s="5" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="5" t="s">
+    <row r="40" spans="2:7">
+      <c r="B40" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="C40" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="D40" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="E40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E40" s="5" t="s">
+      <c r="F40" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="G40" s="5" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="5" t="s">
+    <row r="41" spans="2:7">
+      <c r="B41" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="C41" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="E41" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="F41" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="G41" s="5" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="5" t="s">
+    <row r="42" spans="2:7">
+      <c r="B42" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="D42" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="E42" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="F42" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="G42" s="5" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="5" t="s">
+    <row r="43" spans="2:7">
+      <c r="B43" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="D43" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="E43" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E43" s="5" t="s">
+      <c r="F43" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="G43" s="5" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="5" t="s">
+    <row r="44" spans="2:7">
+      <c r="B44" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="C44" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="D44" s="5" t="s">
         <v>570</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="E44" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="F44" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="G44" s="5" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="5" t="s">
+    <row r="45" spans="2:7">
+      <c r="B45" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="C45" s="5" t="s">
         <v>573</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="D45" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="E45" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="F45" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="G45" s="5" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="5" t="s">
+    <row r="46" spans="2:7">
+      <c r="B46" s="5" t="s">
         <v>576</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>577</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="D46" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="E46" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E46" s="5" t="s">
+      <c r="F46" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="G46" s="5" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="5" t="s">
+    <row r="47" spans="2:7">
+      <c r="B47" s="5" t="s">
         <v>580</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="C47" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="D47" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="E47" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E47" s="5" t="s">
+      <c r="F47" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="G47" s="5" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="5" t="s">
+    <row r="48" spans="2:7">
+      <c r="B48" s="5" t="s">
         <v>584</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="C48" s="5" t="s">
         <v>585</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="D48" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="E48" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E48" s="5" t="s">
+      <c r="F48" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="G48" s="5" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="5" t="s">
+    <row r="49" spans="2:7">
+      <c r="B49" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="C49" s="5" t="s">
         <v>589</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="D49" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="E49" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E49" s="5" t="s">
+      <c r="F49" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="G49" s="5" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="5" t="s">
+    <row r="50" spans="2:7">
+      <c r="B50" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="C50" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="D50" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="E50" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E50" s="5" t="s">
+      <c r="F50" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="G50" s="5" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="5" t="s">
+    <row r="51" spans="2:7">
+      <c r="B51" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="C51" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="D51" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="E51" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="F51" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="G51" s="5" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="5" t="s">
+    <row r="52" spans="2:7">
+      <c r="B52" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="C52" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="D52" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="E52" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E52" s="5" t="s">
+      <c r="F52" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="F52" s="5" t="s">
+      <c r="G52" s="5" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
-      <c r="A53" s="5" t="s">
+    <row r="53" spans="2:7">
+      <c r="B53" s="5" t="s">
         <v>603</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="C53" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="D53" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="E53" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="F53" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="G53" s="5" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="5" t="s">
+    <row r="54" spans="2:7">
+      <c r="B54" s="5" t="s">
         <v>606</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="C54" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="D54" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="E54" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E54" s="5" t="s">
+      <c r="F54" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="G54" s="5" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="5" t="s">
+    <row r="55" spans="2:7">
+      <c r="B55" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="C55" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="D55" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="E55" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E55" s="5" t="s">
+      <c r="F55" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="G55" s="5" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="5" t="s">
+    <row r="56" spans="2:7">
+      <c r="B56" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="C56" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="D56" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="E56" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E56" s="5" t="s">
+      <c r="F56" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="G56" s="5" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="5" t="s">
+    <row r="57" spans="2:7">
+      <c r="B57" s="5" t="s">
         <v>615</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="C57" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="D57" s="5" t="s">
         <v>617</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="E57" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E57" s="5" t="s">
+      <c r="F57" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="G57" s="5" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="A58" s="5" t="s">
+    <row r="58" spans="2:7">
+      <c r="B58" s="5" t="s">
         <v>618</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="C58" s="5" t="s">
         <v>619</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>620</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="E58" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="F58" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="G58" s="5" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="5" t="s">
+    <row r="59" spans="2:7">
+      <c r="B59" s="5" t="s">
         <v>622</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="C59" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="D59" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="E59" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E59" s="5" t="s">
+      <c r="F59" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="G59" s="5" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="5" t="s">
+    <row r="60" spans="2:7">
+      <c r="B60" s="5" t="s">
         <v>626</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="C60" s="5" t="s">
         <v>627</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="D60" s="5" t="s">
         <v>628</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="E60" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E60" s="5" t="s">
+      <c r="F60" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="G60" s="5" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="5" t="s">
+    <row r="61" spans="2:7">
+      <c r="B61" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="C61" s="5" t="s">
         <v>631</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="D61" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="E61" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="F61" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="G61" s="5" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="5" t="s">
+    <row r="62" spans="2:7">
+      <c r="B62" s="5" t="s">
         <v>634</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="C62" s="5" t="s">
         <v>635</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="D62" s="5" t="s">
         <v>636</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="E62" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E62" s="5" t="s">
+      <c r="F62" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="G62" s="5" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="5" t="s">
+    <row r="63" spans="2:7">
+      <c r="B63" s="5" t="s">
         <v>638</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="C63" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="D63" s="5" t="s">
         <v>640</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="E63" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E63" s="5" t="s">
+      <c r="F63" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="G63" s="5" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="5" t="s">
+    <row r="64" spans="2:7">
+      <c r="B64" s="5" t="s">
         <v>642</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="C64" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="D64" s="5" t="s">
         <v>644</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="E64" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E64" s="5" t="s">
+      <c r="F64" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="F64" s="5" t="s">
+      <c r="G64" s="5" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
-      <c r="A65" s="5" t="s">
+    <row r="65" spans="2:7">
+      <c r="B65" s="5" t="s">
         <v>646</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="C65" s="5" t="s">
         <v>647</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="D65" s="5" t="s">
         <v>648</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="E65" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="F65" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="F65" s="5" t="s">
+      <c r="G65" s="5" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
-      <c r="A66" s="5" t="s">
+    <row r="66" spans="2:7">
+      <c r="B66" s="5" t="s">
         <v>650</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="C66" s="5" t="s">
         <v>651</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="D66" s="5" t="s">
         <v>652</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="E66" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="F66" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="F66" s="5" t="s">
+      <c r="G66" s="5" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="5" t="s">
+    <row r="67" spans="2:7">
+      <c r="B67" s="5" t="s">
         <v>654</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="C67" s="5" t="s">
         <v>655</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="D67" s="5" t="s">
         <v>656</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="E67" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="F67" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="F67" s="5" t="s">
+      <c r="G67" s="5" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="A68" s="5" t="s">
+    <row r="68" spans="2:7">
+      <c r="B68" s="5" t="s">
         <v>658</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="C68" s="5" t="s">
         <v>659</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="D68" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="D68" s="5" t="s">
+      <c r="E68" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E68" s="5" t="s">
+      <c r="F68" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="F68" s="5" t="s">
+      <c r="G68" s="5" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
-      <c r="A69" s="5" t="s">
+    <row r="69" spans="2:7">
+      <c r="B69" s="5" t="s">
         <v>662</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="C69" s="5" t="s">
         <v>663</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="D69" s="5" t="s">
         <v>664</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="E69" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="F69" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="G69" s="5" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
-      <c r="A70" s="5" t="s">
+    <row r="70" spans="2:7">
+      <c r="B70" s="5" t="s">
         <v>666</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="C70" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="D70" s="5" t="s">
         <v>668</v>
       </c>
-      <c r="D70" s="5" t="s">
+      <c r="E70" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E70" s="5" t="s">
+      <c r="F70" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="F70" s="5" t="s">
+      <c r="G70" s="5" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
-      <c r="A71" s="5" t="s">
+    <row r="71" spans="2:7">
+      <c r="B71" s="5" t="s">
         <v>670</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="C71" s="5" t="s">
         <v>671</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="D71" s="5" t="s">
         <v>672</v>
       </c>
-      <c r="D71" s="5" t="s">
+      <c r="E71" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="F71" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="F71" s="5" t="s">
+      <c r="G71" s="5" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="A72" s="5" t="s">
+    <row r="72" spans="2:7">
+      <c r="B72" s="5" t="s">
         <v>674</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="C72" s="5" t="s">
         <v>675</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="D72" s="5" t="s">
         <v>676</v>
       </c>
-      <c r="D72" s="5" t="s">
+      <c r="E72" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E72" s="5" t="s">
+      <c r="F72" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="F72" s="5" t="s">
+      <c r="G72" s="5" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
-      <c r="A73" s="5" t="s">
+    <row r="73" spans="2:7">
+      <c r="B73" s="5" t="s">
         <v>678</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="C73" s="5" t="s">
         <v>679</v>
       </c>
-      <c r="C73" s="5" t="s">
+      <c r="D73" s="5" t="s">
         <v>680</v>
       </c>
-      <c r="D73" s="5" t="s">
+      <c r="E73" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="F73" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="F73" s="5" t="s">
+      <c r="G73" s="5" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
-      <c r="A74" s="5" t="s">
+    <row r="74" spans="2:7">
+      <c r="B74" s="5" t="s">
         <v>681</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="C74" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="D74" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="E74" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E74" s="5" t="s">
+      <c r="F74" s="5" t="s">
         <v>401</v>
       </c>
-      <c r="F74" s="5" t="s">
+      <c r="G74" s="5" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
-      <c r="A75" s="5" t="s">
+    <row r="75" spans="2:7">
+      <c r="B75" s="5" t="s">
         <v>684</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="C75" s="5" t="s">
         <v>685</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="D75" s="5" t="s">
         <v>686</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="E75" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E75" s="5" t="s">
+      <c r="F75" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="F75" s="5" t="s">
+      <c r="G75" s="5" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="A76" s="5" t="s">
+    <row r="76" spans="2:7">
+      <c r="B76" s="5" t="s">
         <v>687</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="C76" s="5" t="s">
         <v>688</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="D76" s="5" t="s">
         <v>689</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="E76" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E76" s="5" t="s">
+      <c r="F76" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="F76" s="5" t="s">
+      <c r="G76" s="5" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
-      <c r="A77" s="5" t="s">
+    <row r="77" spans="2:7">
+      <c r="B77" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="C77" s="5" t="s">
         <v>691</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="D77" s="5" t="s">
         <v>692</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="E77" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E77" s="5" t="s">
+      <c r="F77" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="F77" s="5" t="s">
+      <c r="G77" s="5" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
-      <c r="A78" s="5" t="s">
+    <row r="78" spans="2:7">
+      <c r="B78" s="5" t="s">
         <v>693</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="C78" s="5" t="s">
         <v>694</v>
       </c>
-      <c r="C78" s="5" t="s">
+      <c r="D78" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="D78" s="5" t="s">
+      <c r="E78" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E78" s="5" t="s">
+      <c r="F78" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="F78" s="5" t="s">
+      <c r="G78" s="5" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
-      <c r="A79" s="5" t="s">
+    <row r="79" spans="2:7">
+      <c r="B79" s="5" t="s">
         <v>696</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="C79" s="5" t="s">
         <v>697</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="D79" s="5" t="s">
         <v>698</v>
       </c>
-      <c r="D79" s="5" t="s">
+      <c r="E79" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E79" s="5" t="s">
+      <c r="F79" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="F79" s="5" t="s">
+      <c r="G79" s="5" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="5" t="s">
+    <row r="80" spans="2:7">
+      <c r="B80" s="5" t="s">
         <v>699</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="C80" s="5" t="s">
         <v>700</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="D80" s="5" t="s">
         <v>701</v>
       </c>
-      <c r="D80" s="5" t="s">
+      <c r="E80" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E80" s="5" t="s">
+      <c r="F80" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="F80" s="5" t="s">
+      <c r="G80" s="5" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
-      <c r="A81" s="5" t="s">
+    <row r="81" spans="2:7">
+      <c r="B81" s="5" t="s">
         <v>702</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="C81" s="5" t="s">
         <v>703</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="D81" s="5" t="s">
         <v>704</v>
       </c>
-      <c r="D81" s="5" t="s">
+      <c r="E81" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E81" s="5" t="s">
+      <c r="F81" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="F81" s="5" t="s">
+      <c r="G81" s="5" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
-      <c r="A82" s="5" t="s">
+    <row r="82" spans="2:7">
+      <c r="B82" s="5" t="s">
         <v>705</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="C82" s="5" t="s">
         <v>706</v>
       </c>
-      <c r="C82" s="5" t="s">
+      <c r="D82" s="5" t="s">
         <v>707</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="E82" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E82" s="5" t="s">
+      <c r="F82" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="F82" s="5" t="s">
+      <c r="G82" s="5" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
-      <c r="A83" s="5" t="s">
+    <row r="83" spans="2:7">
+      <c r="B83" s="5" t="s">
         <v>708</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="C83" s="5" t="s">
         <v>709</v>
       </c>
-      <c r="C83" s="5" t="s">
+      <c r="D83" s="5" t="s">
         <v>710</v>
       </c>
-      <c r="D83" s="5" t="s">
+      <c r="E83" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E83" s="5" t="s">
+      <c r="F83" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="F83" s="5" t="s">
+      <c r="G83" s="5" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
-      <c r="A84" s="5" t="s">
+    <row r="84" spans="2:7">
+      <c r="B84" s="5" t="s">
         <v>711</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="C84" s="5" t="s">
         <v>712</v>
       </c>
-      <c r="C84" s="5" t="s">
+      <c r="D84" s="5" t="s">
         <v>713</v>
       </c>
-      <c r="D84" s="5" t="s">
+      <c r="E84" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E84" s="5" t="s">
+      <c r="F84" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="F84" s="5" t="s">
+      <c r="G84" s="5" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="5" t="s">
+    <row r="85" spans="2:7">
+      <c r="B85" s="5" t="s">
         <v>714</v>
       </c>
-      <c r="B85" s="5" t="s">
+      <c r="C85" s="5" t="s">
         <v>715</v>
       </c>
-      <c r="C85" s="5" t="s">
+      <c r="D85" s="5" t="s">
         <v>716</v>
       </c>
-      <c r="D85" s="5" t="s">
+      <c r="E85" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E85" s="5" t="s">
+      <c r="F85" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="F85" s="5" t="s">
+      <c r="G85" s="5" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
-      <c r="A86" s="5" t="s">
+    <row r="86" spans="2:7">
+      <c r="B86" s="5" t="s">
         <v>717</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="C86" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="C86" s="5" t="s">
+      <c r="D86" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="D86" s="5" t="s">
+      <c r="E86" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E86" s="5" t="s">
+      <c r="F86" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="F86" s="5" t="s">
+      <c r="G86" s="5" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
-      <c r="A87" s="5" t="s">
+    <row r="87" spans="2:7">
+      <c r="B87" s="5" t="s">
         <v>720</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="C87" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="C87" s="5" t="s">
+      <c r="D87" s="5" t="s">
         <v>722</v>
       </c>
-      <c r="D87" s="5" t="s">
+      <c r="E87" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E87" s="5" t="s">
+      <c r="F87" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="F87" s="5" t="s">
+      <c r="G87" s="5" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
-      <c r="A88" s="5" t="s">
+    <row r="88" spans="2:7">
+      <c r="B88" s="5" t="s">
         <v>723</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="C88" s="5" t="s">
         <v>724</v>
       </c>
-      <c r="C88" s="5" t="s">
+      <c r="D88" s="5" t="s">
         <v>725</v>
       </c>
-      <c r="D88" s="5" t="s">
+      <c r="E88" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E88" s="5" t="s">
+      <c r="F88" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="F88" s="5" t="s">
+      <c r="G88" s="5" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
-      <c r="A89" s="5" t="s">
+    <row r="89" spans="2:7">
+      <c r="B89" s="5" t="s">
         <v>726</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="C89" s="5" t="s">
         <v>727</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="D89" s="5" t="s">
         <v>728</v>
       </c>
-      <c r="D89" s="5" t="s">
+      <c r="E89" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E89" s="5" t="s">
+      <c r="F89" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="F89" s="5" t="s">
+      <c r="G89" s="5" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
-      <c r="A90" s="5" t="s">
+    <row r="90" spans="2:7">
+      <c r="B90" s="5" t="s">
         <v>729</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="C90" s="5" t="s">
         <v>730</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="D90" s="5" t="s">
         <v>731</v>
       </c>
-      <c r="D90" s="5" t="s">
+      <c r="E90" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="E90" s="5" t="s">
+      <c r="F90" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="F90" s="5" t="s">
+      <c r="G90" s="5" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
-      <c r="A91" s="5" t="s">
+    <row r="91" spans="2:7">
+      <c r="B91" s="5" t="s">
         <v>732</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="C91" s="5" t="s">
         <v>733</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="D91" s="5" t="s">
         <v>734</v>
       </c>
-      <c r="D91" s="5" t="s">
+      <c r="E91" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E91" s="5" t="s">
+      <c r="F91" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="F91" s="5" t="s">
+      <c r="G91" s="5" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
-      <c r="A92" s="5" t="s">
+    <row r="92" spans="2:7">
+      <c r="B92" s="5" t="s">
         <v>735</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="C92" s="5" t="s">
         <v>736</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="D92" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="D92" s="5" t="s">
+      <c r="E92" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E92" s="5" t="s">
+      <c r="F92" s="5" t="s">
         <v>397</v>
       </c>
-      <c r="F92" s="5" t="s">
+      <c r="G92" s="5" t="s">
         <v>533</v>
       </c>
     </row>
@@ -10175,604 +10175,604 @@
       <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>744</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>745</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>746</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>747</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>750</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>751</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>752</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>753</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>754</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>755</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>756</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>757</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>759</v>
       </c>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="F16" s="5"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="5" t="s">
         <v>760</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>761</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>762</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>763</v>
       </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="5" t="s">
         <v>764</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>765</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>766</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="5" t="s">
         <v>768</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>769</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>770</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>771</v>
       </c>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="F19" s="5"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="5" t="s">
         <v>772</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>774</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>775</v>
       </c>
-      <c r="E20" s="5"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="F20" s="5"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="5" t="s">
         <v>776</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>777</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>778</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>779</v>
       </c>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="F21" s="5"/>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>781</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>782</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>783</v>
       </c>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="F22" s="5"/>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="5" t="s">
         <v>784</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>785</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>786</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>787</v>
       </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="F23" s="5"/>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="5" t="s">
         <v>788</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>789</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>790</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>791</v>
       </c>
-      <c r="E24" s="5"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="F24" s="5"/>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="5" t="s">
         <v>792</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>793</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>794</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>795</v>
       </c>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="5" t="s">
         <v>796</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>797</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>798</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>799</v>
       </c>
-      <c r="E26" s="5"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="F26" s="5"/>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" s="5" t="s">
         <v>800</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>801</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>802</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>803</v>
       </c>
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="F27" s="5"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>805</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>806</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="5" t="s">
         <v>807</v>
       </c>
-      <c r="E28" s="5"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="F28" s="5"/>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="5" t="s">
         <v>809</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>810</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>811</v>
       </c>
-      <c r="E29" s="5"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="F29" s="5"/>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="5" t="s">
         <v>812</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>813</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>814</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="E30" s="5" t="s">
         <v>815</v>
       </c>
-      <c r="E30" s="5"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="F30" s="5"/>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>817</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>818</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>819</v>
       </c>
-      <c r="E31" s="5"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="F31" s="5"/>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="5" t="s">
         <v>820</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>821</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>822</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="E32" s="5" t="s">
         <v>823</v>
       </c>
-      <c r="E32" s="5"/>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="F32" s="5"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="5" t="s">
         <v>824</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>825</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="D33" s="5" t="s">
         <v>826</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="E33" s="5" t="s">
         <v>827</v>
       </c>
-      <c r="E33" s="5"/>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="F33" s="5"/>
+    </row>
+    <row r="34" spans="2:6">
+      <c r="B34" s="5" t="s">
         <v>828</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>829</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>830</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="E34" s="5" t="s">
         <v>831</v>
       </c>
-      <c r="E34" s="5"/>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="F34" s="5"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="5" t="s">
         <v>832</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="5" t="s">
         <v>833</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>834</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>835</v>
       </c>
-      <c r="E35" s="5"/>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="F35" s="5"/>
+    </row>
+    <row r="36" spans="2:6">
+      <c r="B36" s="5" t="s">
         <v>836</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>837</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>838</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="E36" s="5" t="s">
         <v>839</v>
       </c>
-      <c r="E36" s="5"/>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="F36" s="5"/>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="5" t="s">
         <v>840</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="C37" s="5" t="s">
         <v>841</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="D37" s="5" t="s">
         <v>842</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="E37" s="5" t="s">
         <v>843</v>
       </c>
-      <c r="E37" s="5"/>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="F37" s="5"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="5" t="s">
         <v>844</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="C38" s="5" t="s">
         <v>845</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>846</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="E38" s="5" t="s">
         <v>847</v>
       </c>
-      <c r="E38" s="5"/>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="F38" s="5"/>
+    </row>
+    <row r="39" spans="2:6">
+      <c r="B39" s="5" t="s">
         <v>848</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="C39" s="5" t="s">
         <v>849</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>850</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="E39" s="5" t="s">
         <v>851</v>
       </c>
-      <c r="E39" s="5"/>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="F39" s="5"/>
+    </row>
+    <row r="40" spans="2:6">
+      <c r="B40" s="5" t="s">
         <v>852</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="C40" s="5" t="s">
         <v>853</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="D40" s="5" t="s">
         <v>854</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="E40" s="5" t="s">
         <v>855</v>
       </c>
-      <c r="E40" s="5"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="F40" s="5"/>
+    </row>
+    <row r="41" spans="2:6">
+      <c r="B41" s="5" t="s">
         <v>856</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="C41" s="5" t="s">
         <v>857</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>858</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="E41" s="5" t="s">
         <v>859</v>
       </c>
-      <c r="E41" s="5"/>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="F41" s="5"/>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" s="5" t="s">
         <v>860</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>861</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="D42" s="5" t="s">
         <v>862</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="E42" s="5" t="s">
         <v>863</v>
       </c>
-      <c r="E42" s="5"/>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="F42" s="5"/>
+    </row>
+    <row r="43" spans="2:6">
+      <c r="B43" s="5" t="s">
         <v>864</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>865</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="D43" s="5" t="s">
         <v>866</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="E43" s="5" t="s">
         <v>867</v>
       </c>
-      <c r="E43" s="5"/>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="F43" s="5"/>
+    </row>
+    <row r="44" spans="2:6">
+      <c r="B44" s="5" t="s">
         <v>868</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="C44" s="5" t="s">
         <v>869</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="D44" s="5" t="s">
         <v>870</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="E44" s="5" t="s">
         <v>871</v>
       </c>
-      <c r="E44" s="5"/>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
+      <c r="F44" s="5"/>
+    </row>
+    <row r="45" spans="2:6">
+      <c r="B45" s="5" t="s">
         <v>872</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="C45" s="5" t="s">
         <v>873</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="D45" s="5" t="s">
         <v>874</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="E45" s="5" t="s">
         <v>875</v>
       </c>
-      <c r="E45" s="5"/>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
+      <c r="F45" s="5"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="5" t="s">
         <v>876</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>877</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="D46" s="5" t="s">
         <v>878</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="E46" s="5" t="s">
         <v>879</v>
       </c>
-      <c r="E46" s="5"/>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
+      <c r="F46" s="5"/>
+    </row>
+    <row r="47" spans="2:6">
+      <c r="B47" s="5" t="s">
         <v>880</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="C47" s="5" t="s">
         <v>881</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="D47" s="5" t="s">
         <v>882</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="E47" s="5" t="s">
         <v>883</v>
       </c>
-      <c r="E47" s="5"/>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
+      <c r="F47" s="5"/>
+    </row>
+    <row r="48" spans="2:6">
+      <c r="B48" s="5" t="s">
         <v>884</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="C48" s="5" t="s">
         <v>885</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="D48" s="5" t="s">
         <v>886</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="E48" s="5" t="s">
         <v>887</v>
       </c>
-      <c r="E48" s="5"/>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
+      <c r="F48" s="5"/>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="5" t="s">
         <v>888</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="C49" s="5" t="s">
         <v>889</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="D49" s="5" t="s">
         <v>890</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="E49" s="5" t="s">
         <v>891</v>
       </c>
-      <c r="E49" s="5"/>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
+      <c r="F49" s="5"/>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="5" t="s">
         <v>892</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="C50" s="5" t="s">
         <v>893</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="D50" s="5" t="s">
         <v>894</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="E50" s="5" t="s">
         <v>895</v>
       </c>
-      <c r="E50" s="5"/>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
+      <c r="F50" s="5"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="5" t="s">
         <v>896</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="C51" s="5" t="s">
         <v>897</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="D51" s="5" t="s">
         <v>898</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="E51" s="5" t="s">
         <v>899</v>
       </c>
-      <c r="E51" s="5"/>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
+      <c r="F51" s="5"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="5" t="s">
         <v>900</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="C52" s="5" t="s">
         <v>901</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="D52" s="5" t="s">
         <v>902</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="E52" s="5" t="s">
         <v>903</v>
       </c>
-      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10923,1122 +10923,1122 @@
       <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>744</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>908</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="5" t="s">
+      <c r="B14" s="5" t="s">
         <v>744</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>909</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>909</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>910</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="2:5">
+      <c r="B17" s="5" t="s">
         <v>752</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>910</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="2:5">
+      <c r="B18" s="5" t="s">
         <v>752</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>911</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="2:5">
+      <c r="B19" s="5" t="s">
         <v>756</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>911</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="2:5">
+      <c r="B20" s="5" t="s">
         <v>756</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>912</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="2:5">
+      <c r="B21" s="5" t="s">
         <v>760</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>912</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="2:5">
+      <c r="B22" s="5" t="s">
         <v>760</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>913</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="2:5">
+      <c r="B23" s="5" t="s">
         <v>764</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>913</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="2:5">
+      <c r="B24" s="5" t="s">
         <v>764</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="2:5">
+      <c r="B25" s="5" t="s">
         <v>768</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="2:5">
+      <c r="B26" s="5" t="s">
         <v>768</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="2:5">
+      <c r="B27" s="5" t="s">
         <v>772</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="2:5">
+      <c r="B28" s="5" t="s">
         <v>772</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="D28" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="2:5">
+      <c r="B29" s="5" t="s">
         <v>776</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="C29" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="2:5">
+      <c r="B30" s="5" t="s">
         <v>776</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="E30" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="5" t="s">
+    <row r="31" spans="2:5">
+      <c r="B31" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="2:5">
+      <c r="B32" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="C32" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="E32" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="5" t="s">
+    <row r="33" spans="2:5">
+      <c r="B33" s="5" t="s">
         <v>784</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="D33" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="E33" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="2:5">
+      <c r="B34" s="5" t="s">
         <v>784</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="C34" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="D34" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="E34" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="5" t="s">
+    <row r="35" spans="2:5">
+      <c r="B35" s="5" t="s">
         <v>788</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="5" t="s">
+    <row r="36" spans="2:5">
+      <c r="B36" s="5" t="s">
         <v>788</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="C36" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="D36" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="E36" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="5" t="s">
+    <row r="37" spans="2:5">
+      <c r="B37" s="5" t="s">
         <v>792</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="C37" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="D37" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="E37" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="5" t="s">
+    <row r="38" spans="2:5">
+      <c r="B38" s="5" t="s">
         <v>792</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="C38" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="D38" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="E38" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="5" t="s">
+    <row r="39" spans="2:5">
+      <c r="B39" s="5" t="s">
         <v>796</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="C39" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="E39" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="5" t="s">
+    <row r="40" spans="2:5">
+      <c r="B40" s="5" t="s">
         <v>796</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="C40" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="D40" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="E40" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="5" t="s">
+    <row r="41" spans="2:5">
+      <c r="B41" s="5" t="s">
         <v>800</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="C41" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="D41" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="E41" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
-      <c r="A42" s="5" t="s">
+    <row r="42" spans="2:5">
+      <c r="B42" s="5" t="s">
         <v>800</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="C42" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="D42" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="E42" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="5" t="s">
+    <row r="43" spans="2:5">
+      <c r="B43" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="C43" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="D43" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="E43" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="5" t="s">
+    <row r="44" spans="2:5">
+      <c r="B44" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="C44" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="D44" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="E44" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
-      <c r="A45" s="5" t="s">
+    <row r="45" spans="2:5">
+      <c r="B45" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="C45" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="D45" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="E45" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="5" t="s">
+    <row r="46" spans="2:5">
+      <c r="B46" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="C46" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="D46" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="E46" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="5" t="s">
+    <row r="47" spans="2:5">
+      <c r="B47" s="5" t="s">
         <v>812</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="C47" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="D47" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="E47" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="5" t="s">
+    <row r="48" spans="2:5">
+      <c r="B48" s="5" t="s">
         <v>812</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="C48" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="D48" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="E48" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="5" t="s">
+    <row r="49" spans="2:5">
+      <c r="B49" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="C49" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="D49" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="E49" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="5" t="s">
+    <row r="50" spans="2:5">
+      <c r="B50" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="C50" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="D50" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="E50" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="5" t="s">
+    <row r="51" spans="2:5">
+      <c r="B51" s="5" t="s">
         <v>820</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="C51" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="D51" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="E51" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="5" t="s">
+    <row r="52" spans="2:5">
+      <c r="B52" s="5" t="s">
         <v>820</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="C52" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="D52" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="E52" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
-      <c r="A53" s="5" t="s">
+    <row r="53" spans="2:5">
+      <c r="B53" s="5" t="s">
         <v>824</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="C53" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="D53" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="E53" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
-      <c r="A54" s="5" t="s">
+    <row r="54" spans="2:5">
+      <c r="B54" s="5" t="s">
         <v>824</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="C54" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="D54" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="E54" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="5" t="s">
+    <row r="55" spans="2:5">
+      <c r="B55" s="5" t="s">
         <v>828</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="C55" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="D55" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="E55" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="5" t="s">
+    <row r="56" spans="2:5">
+      <c r="B56" s="5" t="s">
         <v>828</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="C56" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="D56" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="E56" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="5" t="s">
+    <row r="57" spans="2:5">
+      <c r="B57" s="5" t="s">
         <v>832</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="C57" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="D57" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="E57" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="5" t="s">
+    <row r="58" spans="2:5">
+      <c r="B58" s="5" t="s">
         <v>832</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="C58" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="E58" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="5" t="s">
+    <row r="59" spans="2:5">
+      <c r="B59" s="5" t="s">
         <v>836</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="C59" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="D59" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="E59" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="5" t="s">
+    <row r="60" spans="2:5">
+      <c r="B60" s="5" t="s">
         <v>836</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="C60" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="D60" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="E60" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="5" t="s">
+    <row r="61" spans="2:5">
+      <c r="B61" s="5" t="s">
         <v>840</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="C61" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="D61" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="E61" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="5" t="s">
+    <row r="62" spans="2:5">
+      <c r="B62" s="5" t="s">
         <v>840</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="C62" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="D62" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="E62" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="5" t="s">
+    <row r="63" spans="2:5">
+      <c r="B63" s="5" t="s">
         <v>844</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="C63" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="D63" s="5" t="s">
         <v>467</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="E63" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="5" t="s">
+    <row r="64" spans="2:5">
+      <c r="B64" s="5" t="s">
         <v>844</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="C64" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="D64" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="E64" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="5" t="s">
+    <row r="65" spans="2:5">
+      <c r="B65" s="5" t="s">
         <v>848</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="C65" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="D65" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="E65" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="5" t="s">
+    <row r="66" spans="2:5">
+      <c r="B66" s="5" t="s">
         <v>848</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="C66" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="D66" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="E66" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="5" t="s">
+    <row r="67" spans="2:5">
+      <c r="B67" s="5" t="s">
         <v>852</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="C67" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="D67" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="E67" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="5" t="s">
+    <row r="68" spans="2:5">
+      <c r="B68" s="5" t="s">
         <v>852</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="C68" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="D68" s="5" t="s">
         <v>914</v>
       </c>
-      <c r="D68" s="5" t="s">
+      <c r="E68" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="5" t="s">
+    <row r="69" spans="2:5">
+      <c r="B69" s="5" t="s">
         <v>856</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="C69" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="D69" s="5" t="s">
         <v>914</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="E69" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="5" t="s">
+    <row r="70" spans="2:5">
+      <c r="B70" s="5" t="s">
         <v>856</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="C70" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="D70" s="5" t="s">
         <v>915</v>
       </c>
-      <c r="D70" s="5" t="s">
+      <c r="E70" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="5" t="s">
+    <row r="71" spans="2:5">
+      <c r="B71" s="5" t="s">
         <v>860</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="C71" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="D71" s="5" t="s">
         <v>915</v>
       </c>
-      <c r="D71" s="5" t="s">
+      <c r="E71" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="5" t="s">
+    <row r="72" spans="2:5">
+      <c r="B72" s="5" t="s">
         <v>860</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="C72" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="D72" s="5" t="s">
         <v>916</v>
       </c>
-      <c r="D72" s="5" t="s">
+      <c r="E72" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="5" t="s">
+    <row r="73" spans="2:5">
+      <c r="B73" s="5" t="s">
         <v>864</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="C73" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C73" s="5" t="s">
+      <c r="D73" s="5" t="s">
         <v>916</v>
       </c>
-      <c r="D73" s="5" t="s">
+      <c r="E73" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="5" t="s">
+    <row r="74" spans="2:5">
+      <c r="B74" s="5" t="s">
         <v>864</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="C74" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="D74" s="5" t="s">
         <v>917</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="E74" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="5" t="s">
+    <row r="75" spans="2:5">
+      <c r="B75" s="5" t="s">
         <v>868</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="C75" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="D75" s="5" t="s">
         <v>917</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="E75" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="5" t="s">
+    <row r="76" spans="2:5">
+      <c r="B76" s="5" t="s">
         <v>868</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="C76" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="D76" s="5" t="s">
         <v>918</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="E76" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
-      <c r="A77" s="5" t="s">
+    <row r="77" spans="2:5">
+      <c r="B77" s="5" t="s">
         <v>872</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="C77" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="D77" s="5" t="s">
         <v>918</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="E77" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
-      <c r="A78" s="5" t="s">
+    <row r="78" spans="2:5">
+      <c r="B78" s="5" t="s">
         <v>872</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="C78" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C78" s="5" t="s">
+      <c r="D78" s="5" t="s">
         <v>919</v>
       </c>
-      <c r="D78" s="5" t="s">
+      <c r="E78" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
-      <c r="A79" s="5" t="s">
+    <row r="79" spans="2:5">
+      <c r="B79" s="5" t="s">
         <v>876</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="C79" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="D79" s="5" t="s">
         <v>919</v>
       </c>
-      <c r="D79" s="5" t="s">
+      <c r="E79" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
-      <c r="A80" s="5" t="s">
+    <row r="80" spans="2:5">
+      <c r="B80" s="5" t="s">
         <v>876</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="C80" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="D80" s="5" t="s">
         <v>920</v>
       </c>
-      <c r="D80" s="5" t="s">
+      <c r="E80" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
-      <c r="A81" s="5" t="s">
+    <row r="81" spans="2:5">
+      <c r="B81" s="5" t="s">
         <v>880</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="C81" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="D81" s="5" t="s">
         <v>920</v>
       </c>
-      <c r="D81" s="5" t="s">
+      <c r="E81" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
-      <c r="A82" s="5" t="s">
+    <row r="82" spans="2:5">
+      <c r="B82" s="5" t="s">
         <v>880</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="C82" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C82" s="5" t="s">
+      <c r="D82" s="5" t="s">
         <v>921</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="E82" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
-      <c r="A83" s="5" t="s">
+    <row r="83" spans="2:5">
+      <c r="B83" s="5" t="s">
         <v>884</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="C83" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C83" s="5" t="s">
+      <c r="D83" s="5" t="s">
         <v>921</v>
       </c>
-      <c r="D83" s="5" t="s">
+      <c r="E83" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="5" t="s">
+    <row r="84" spans="2:5">
+      <c r="B84" s="5" t="s">
         <v>884</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="C84" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C84" s="5" t="s">
+      <c r="D84" s="5" t="s">
         <v>922</v>
       </c>
-      <c r="D84" s="5" t="s">
+      <c r="E84" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
-      <c r="A85" s="5" t="s">
+    <row r="85" spans="2:5">
+      <c r="B85" s="5" t="s">
         <v>888</v>
       </c>
-      <c r="B85" s="5" t="s">
+      <c r="C85" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C85" s="5" t="s">
+      <c r="D85" s="5" t="s">
         <v>922</v>
       </c>
-      <c r="D85" s="5" t="s">
+      <c r="E85" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="5" t="s">
+    <row r="86" spans="2:5">
+      <c r="B86" s="5" t="s">
         <v>888</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="C86" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C86" s="5" t="s">
+      <c r="D86" s="5" t="s">
         <v>923</v>
       </c>
-      <c r="D86" s="5" t="s">
+      <c r="E86" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
-      <c r="A87" s="5" t="s">
+    <row r="87" spans="2:5">
+      <c r="B87" s="5" t="s">
         <v>892</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="C87" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C87" s="5" t="s">
+      <c r="D87" s="5" t="s">
         <v>923</v>
       </c>
-      <c r="D87" s="5" t="s">
+      <c r="E87" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="5" t="s">
+    <row r="88" spans="2:5">
+      <c r="B88" s="5" t="s">
         <v>892</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="C88" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C88" s="5" t="s">
+      <c r="D88" s="5" t="s">
         <v>924</v>
       </c>
-      <c r="D88" s="5" t="s">
+      <c r="E88" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="5" t="s">
+    <row r="89" spans="2:5">
+      <c r="B89" s="5" t="s">
         <v>896</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="C89" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="D89" s="5" t="s">
         <v>924</v>
       </c>
-      <c r="D89" s="5" t="s">
+      <c r="E89" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
-      <c r="A90" s="5" t="s">
+    <row r="90" spans="2:5">
+      <c r="B90" s="5" t="s">
         <v>896</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="C90" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="D90" s="5" t="s">
         <v>925</v>
       </c>
-      <c r="D90" s="5" t="s">
+      <c r="E90" s="5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
-      <c r="A91" s="5" t="s">
+    <row r="91" spans="2:5">
+      <c r="B91" s="5" t="s">
         <v>900</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="C91" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="D91" s="5" t="s">
         <v>925</v>
       </c>
-      <c r="D91" s="5" t="s">
+      <c r="E91" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
-      <c r="A92" s="5" t="s">
+    <row r="92" spans="2:5">
+      <c r="B92" s="5" t="s">
         <v>900</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="C92" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="D92" s="5" t="s">
         <v>926</v>
       </c>
-      <c r="D92" s="5" t="s">
+      <c r="E92" s="5" t="s">
         <v>69</v>
       </c>
     </row>

--- a/examples/showcase/data/Battle.xlsx
+++ b/examples/showcase/data/Battle.xlsx
@@ -617,7 +617,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2136,12 +2136,12 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>b0a9bd963cf8bc87</t>
+          <t>d1401fb77a0a2d00</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>required;parser=json</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -2575,12 +2575,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>996fe1623cec07ee</t>
+          <t>34322ffa4454335d</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>required;parser=json</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -3619,7 +3619,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -7758,7 +7758,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -10590,7 +10590,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -10658,7 +10658,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>18e482d6eedb4d5c</t>
+          <t>fd0a7a4819717e3b</t>
         </is>
       </c>
     </row>
@@ -10808,17 +10808,17 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
+          <t>required;parser=json</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>required</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>optional</t>
         </is>
       </c>
     </row>

--- a/examples/showcase/data/Battle.xlsx
+++ b/examples/showcase/data/Battle.xlsx
@@ -262,7 +262,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2373" uniqueCount="976">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2373" uniqueCount="984">
   <si>
     <t>@table</t>
   </si>
@@ -1251,7 +1251,7 @@
     <t>Buff</t>
   </si>
   <si>
-    <t>ab300d6757967f84</t>
+    <t>0b98849d3da9e5fb</t>
   </si>
   <si>
     <t>duration</t>
@@ -1260,346 +1260,370 @@
     <t>modifiers</t>
   </si>
   <si>
+    <t>list&lt;struct&lt;StatModifier&gt;&gt;</t>
+  </si>
+  <si>
+    <t>parser=json;length=1..3</t>
+  </si>
+  <si>
+    <t>6001</t>
+  </si>
+  <si>
+    <t>Buff 6001</t>
+  </si>
+  <si>
+    <t>4s</t>
+  </si>
+  <si>
+    <t>[{"stat":"Attack","value":6,"is_percent":false}]</t>
+  </si>
+  <si>
+    <t>6002</t>
+  </si>
+  <si>
+    <t>Buff 6002</t>
+  </si>
+  <si>
+    <t>5s</t>
+  </si>
+  <si>
+    <t>[{"stat":"Defense","value":7,"is_percent":true}]</t>
+  </si>
+  <si>
+    <t>6003</t>
+  </si>
+  <si>
+    <t>Buff 6003</t>
+  </si>
+  <si>
+    <t>6s</t>
+  </si>
+  <si>
+    <t>[{"stat":"Speed","value":8,"is_percent":false}]</t>
+  </si>
+  <si>
+    <t>6004</t>
+  </si>
+  <si>
+    <t>Buff 6004</t>
+  </si>
+  <si>
+    <t>7s</t>
+  </si>
+  <si>
+    <t>[{"stat":"CritRate","value":9,"is_percent":true}]</t>
+  </si>
+  <si>
+    <t>6005</t>
+  </si>
+  <si>
+    <t>Buff 6005</t>
+  </si>
+  <si>
+    <t>8s</t>
+  </si>
+  <si>
+    <t>[{"stat":"Hp","value":10,"is_percent":false}]</t>
+  </si>
+  <si>
+    <t>6006</t>
+  </si>
+  <si>
+    <t>Buff 6006</t>
+  </si>
+  <si>
+    <t>9s</t>
+  </si>
+  <si>
+    <t>[{"stat":"Attack","value":11,"is_percent":true}]</t>
+  </si>
+  <si>
+    <t>6007</t>
+  </si>
+  <si>
+    <t>Buff 6007</t>
+  </si>
+  <si>
+    <t>10s</t>
+  </si>
+  <si>
+    <t>[{"stat":"Defense","value":12,"is_percent":false}]</t>
+  </si>
+  <si>
+    <t>6008</t>
+  </si>
+  <si>
+    <t>Buff 6008</t>
+  </si>
+  <si>
+    <t>3s</t>
+  </si>
+  <si>
+    <t>[{"stat":"Speed","value":13,"is_percent":true}]</t>
+  </si>
+  <si>
+    <t>6009</t>
+  </si>
+  <si>
+    <t>Buff 6009</t>
+  </si>
+  <si>
+    <t>[{"stat":"CritRate","value":14,"is_percent":false}]</t>
+  </si>
+  <si>
+    <t>6010</t>
+  </si>
+  <si>
+    <t>Buff 6010</t>
+  </si>
+  <si>
+    <t>[{"stat":"Hp","value":15,"is_percent":true}]</t>
+  </si>
+  <si>
+    <t>6011</t>
+  </si>
+  <si>
+    <t>Buff 6011</t>
+  </si>
+  <si>
+    <t>[{"stat":"Attack","value":16,"is_percent":false}]</t>
+  </si>
+  <si>
+    <t>6012</t>
+  </si>
+  <si>
+    <t>Buff 6012</t>
+  </si>
+  <si>
+    <t>[{"stat":"Defense","value":17,"is_percent":true}]</t>
+  </si>
+  <si>
+    <t>6013</t>
+  </si>
+  <si>
+    <t>Buff 6013</t>
+  </si>
+  <si>
+    <t>[{"stat":"Speed","value":18,"is_percent":false}]</t>
+  </si>
+  <si>
+    <t>6014</t>
+  </si>
+  <si>
+    <t>Buff 6014</t>
+  </si>
+  <si>
+    <t>[{"stat":"CritRate","value":19,"is_percent":true}]</t>
+  </si>
+  <si>
+    <t>6015</t>
+  </si>
+  <si>
+    <t>Buff 6015</t>
+  </si>
+  <si>
+    <t>[{"stat":"Hp","value":20,"is_percent":false}]</t>
+  </si>
+  <si>
+    <t>6016</t>
+  </si>
+  <si>
+    <t>Buff 6016</t>
+  </si>
+  <si>
+    <t>[{"stat":"Attack","value":21,"is_percent":true}]</t>
+  </si>
+  <si>
+    <t>6017</t>
+  </si>
+  <si>
+    <t>Buff 6017</t>
+  </si>
+  <si>
+    <t>[{"stat":"Defense","value":22,"is_percent":false}]</t>
+  </si>
+  <si>
+    <t>6018</t>
+  </si>
+  <si>
+    <t>Buff 6018</t>
+  </si>
+  <si>
+    <t>[{"stat":"Speed","value":23,"is_percent":true}]</t>
+  </si>
+  <si>
+    <t>6019</t>
+  </si>
+  <si>
+    <t>Buff 6019</t>
+  </si>
+  <si>
+    <t>[{"stat":"CritRate","value":24,"is_percent":false}]</t>
+  </si>
+  <si>
+    <t>6020</t>
+  </si>
+  <si>
+    <t>Buff 6020</t>
+  </si>
+  <si>
+    <t>[{"stat":"Hp","value":5,"is_percent":true}]</t>
+  </si>
+  <si>
+    <t>DropGroup</t>
+  </si>
+  <si>
+    <t>ddc8f184c6f4ca0b</t>
+  </si>
+  <si>
+    <t>7001</t>
+  </si>
+  <si>
+    <t>Drop Group 7001</t>
+  </si>
+  <si>
+    <t>7002</t>
+  </si>
+  <si>
+    <t>Drop Group 7002</t>
+  </si>
+  <si>
+    <t>7003</t>
+  </si>
+  <si>
+    <t>Drop Group 7003</t>
+  </si>
+  <si>
+    <t>7004</t>
+  </si>
+  <si>
+    <t>Drop Group 7004</t>
+  </si>
+  <si>
+    <t>7005</t>
+  </si>
+  <si>
+    <t>Drop Group 7005</t>
+  </si>
+  <si>
+    <t>7006</t>
+  </si>
+  <si>
+    <t>Drop Group 7006</t>
+  </si>
+  <si>
+    <t>7007</t>
+  </si>
+  <si>
+    <t>Drop Group 7007</t>
+  </si>
+  <si>
+    <t>7008</t>
+  </si>
+  <si>
+    <t>Drop Group 7008</t>
+  </si>
+  <si>
+    <t>7009</t>
+  </si>
+  <si>
+    <t>Drop Group 7009</t>
+  </si>
+  <si>
+    <t>7010</t>
+  </si>
+  <si>
+    <t>Drop Group 7010</t>
+  </si>
+  <si>
+    <t>7011</t>
+  </si>
+  <si>
+    <t>Drop Group 7011</t>
+  </si>
+  <si>
+    <t>7012</t>
+  </si>
+  <si>
+    <t>Drop Group 7012</t>
+  </si>
+  <si>
+    <t>7013</t>
+  </si>
+  <si>
+    <t>Drop Group 7013</t>
+  </si>
+  <si>
+    <t>7014</t>
+  </si>
+  <si>
+    <t>Drop Group 7014</t>
+  </si>
+  <si>
+    <t>7015</t>
+  </si>
+  <si>
+    <t>Drop Group 7015</t>
+  </si>
+  <si>
+    <t>7016</t>
+  </si>
+  <si>
+    <t>Drop Group 7016</t>
+  </si>
+  <si>
+    <t>7017</t>
+  </si>
+  <si>
+    <t>Drop Group 7017</t>
+  </si>
+  <si>
+    <t>7018</t>
+  </si>
+  <si>
+    <t>Drop Group 7018</t>
+  </si>
+  <si>
+    <t>7019</t>
+  </si>
+  <si>
+    <t>Drop Group 7019</t>
+  </si>
+  <si>
+    <t>7020</t>
+  </si>
+  <si>
+    <t>Drop Group 7020</t>
+  </si>
+  <si>
+    <t>DropEntry</t>
+  </si>
+  <si>
+    <t>38e6bc608bd50c74</t>
+  </si>
+  <si>
+    <t>group_id</t>
+  </si>
+  <si>
+    <t>seq</t>
+  </si>
+  <si>
+    <t>item_id</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>ref&lt;DropGroup.id&gt;</t>
+  </si>
+  <si>
+    <t>ref&lt;Item.id&gt;</t>
+  </si>
+  <si>
     <t>f32</t>
-  </si>
-  <si>
-    <t>list&lt;struct&lt;StatModifier&gt;&gt;</t>
-  </si>
-  <si>
-    <t>parser=json;length=1..3</t>
-  </si>
-  <si>
-    <t>6001</t>
-  </si>
-  <si>
-    <t>Buff 6001</t>
-  </si>
-  <si>
-    <t>[{"stat":"Attack","value":6,"is_percent":false}]</t>
-  </si>
-  <si>
-    <t>6002</t>
-  </si>
-  <si>
-    <t>Buff 6002</t>
-  </si>
-  <si>
-    <t>[{"stat":"Defense","value":7,"is_percent":true}]</t>
-  </si>
-  <si>
-    <t>6003</t>
-  </si>
-  <si>
-    <t>Buff 6003</t>
-  </si>
-  <si>
-    <t>[{"stat":"Speed","value":8,"is_percent":false}]</t>
-  </si>
-  <si>
-    <t>6004</t>
-  </si>
-  <si>
-    <t>Buff 6004</t>
-  </si>
-  <si>
-    <t>[{"stat":"CritRate","value":9,"is_percent":true}]</t>
-  </si>
-  <si>
-    <t>6005</t>
-  </si>
-  <si>
-    <t>Buff 6005</t>
-  </si>
-  <si>
-    <t>[{"stat":"Hp","value":10,"is_percent":false}]</t>
-  </si>
-  <si>
-    <t>6006</t>
-  </si>
-  <si>
-    <t>Buff 6006</t>
-  </si>
-  <si>
-    <t>[{"stat":"Attack","value":11,"is_percent":true}]</t>
-  </si>
-  <si>
-    <t>6007</t>
-  </si>
-  <si>
-    <t>Buff 6007</t>
-  </si>
-  <si>
-    <t>[{"stat":"Defense","value":12,"is_percent":false}]</t>
-  </si>
-  <si>
-    <t>6008</t>
-  </si>
-  <si>
-    <t>Buff 6008</t>
-  </si>
-  <si>
-    <t>[{"stat":"Speed","value":13,"is_percent":true}]</t>
-  </si>
-  <si>
-    <t>6009</t>
-  </si>
-  <si>
-    <t>Buff 6009</t>
-  </si>
-  <si>
-    <t>[{"stat":"CritRate","value":14,"is_percent":false}]</t>
-  </si>
-  <si>
-    <t>6010</t>
-  </si>
-  <si>
-    <t>Buff 6010</t>
-  </si>
-  <si>
-    <t>[{"stat":"Hp","value":15,"is_percent":true}]</t>
-  </si>
-  <si>
-    <t>6011</t>
-  </si>
-  <si>
-    <t>Buff 6011</t>
-  </si>
-  <si>
-    <t>[{"stat":"Attack","value":16,"is_percent":false}]</t>
-  </si>
-  <si>
-    <t>6012</t>
-  </si>
-  <si>
-    <t>Buff 6012</t>
-  </si>
-  <si>
-    <t>[{"stat":"Defense","value":17,"is_percent":true}]</t>
-  </si>
-  <si>
-    <t>6013</t>
-  </si>
-  <si>
-    <t>Buff 6013</t>
-  </si>
-  <si>
-    <t>[{"stat":"Speed","value":18,"is_percent":false}]</t>
-  </si>
-  <si>
-    <t>6014</t>
-  </si>
-  <si>
-    <t>Buff 6014</t>
-  </si>
-  <si>
-    <t>[{"stat":"CritRate","value":19,"is_percent":true}]</t>
-  </si>
-  <si>
-    <t>6015</t>
-  </si>
-  <si>
-    <t>Buff 6015</t>
-  </si>
-  <si>
-    <t>[{"stat":"Hp","value":20,"is_percent":false}]</t>
-  </si>
-  <si>
-    <t>6016</t>
-  </si>
-  <si>
-    <t>Buff 6016</t>
-  </si>
-  <si>
-    <t>[{"stat":"Attack","value":21,"is_percent":true}]</t>
-  </si>
-  <si>
-    <t>6017</t>
-  </si>
-  <si>
-    <t>Buff 6017</t>
-  </si>
-  <si>
-    <t>[{"stat":"Defense","value":22,"is_percent":false}]</t>
-  </si>
-  <si>
-    <t>6018</t>
-  </si>
-  <si>
-    <t>Buff 6018</t>
-  </si>
-  <si>
-    <t>[{"stat":"Speed","value":23,"is_percent":true}]</t>
-  </si>
-  <si>
-    <t>6019</t>
-  </si>
-  <si>
-    <t>Buff 6019</t>
-  </si>
-  <si>
-    <t>[{"stat":"CritRate","value":24,"is_percent":false}]</t>
-  </si>
-  <si>
-    <t>6020</t>
-  </si>
-  <si>
-    <t>Buff 6020</t>
-  </si>
-  <si>
-    <t>[{"stat":"Hp","value":5,"is_percent":true}]</t>
-  </si>
-  <si>
-    <t>DropGroup</t>
-  </si>
-  <si>
-    <t>ddc8f184c6f4ca0b</t>
-  </si>
-  <si>
-    <t>7001</t>
-  </si>
-  <si>
-    <t>Drop Group 7001</t>
-  </si>
-  <si>
-    <t>7002</t>
-  </si>
-  <si>
-    <t>Drop Group 7002</t>
-  </si>
-  <si>
-    <t>7003</t>
-  </si>
-  <si>
-    <t>Drop Group 7003</t>
-  </si>
-  <si>
-    <t>7004</t>
-  </si>
-  <si>
-    <t>Drop Group 7004</t>
-  </si>
-  <si>
-    <t>7005</t>
-  </si>
-  <si>
-    <t>Drop Group 7005</t>
-  </si>
-  <si>
-    <t>7006</t>
-  </si>
-  <si>
-    <t>Drop Group 7006</t>
-  </si>
-  <si>
-    <t>7007</t>
-  </si>
-  <si>
-    <t>Drop Group 7007</t>
-  </si>
-  <si>
-    <t>7008</t>
-  </si>
-  <si>
-    <t>Drop Group 7008</t>
-  </si>
-  <si>
-    <t>7009</t>
-  </si>
-  <si>
-    <t>Drop Group 7009</t>
-  </si>
-  <si>
-    <t>7010</t>
-  </si>
-  <si>
-    <t>Drop Group 7010</t>
-  </si>
-  <si>
-    <t>7011</t>
-  </si>
-  <si>
-    <t>Drop Group 7011</t>
-  </si>
-  <si>
-    <t>7012</t>
-  </si>
-  <si>
-    <t>Drop Group 7012</t>
-  </si>
-  <si>
-    <t>7013</t>
-  </si>
-  <si>
-    <t>Drop Group 7013</t>
-  </si>
-  <si>
-    <t>7014</t>
-  </si>
-  <si>
-    <t>Drop Group 7014</t>
-  </si>
-  <si>
-    <t>7015</t>
-  </si>
-  <si>
-    <t>Drop Group 7015</t>
-  </si>
-  <si>
-    <t>7016</t>
-  </si>
-  <si>
-    <t>Drop Group 7016</t>
-  </si>
-  <si>
-    <t>7017</t>
-  </si>
-  <si>
-    <t>Drop Group 7017</t>
-  </si>
-  <si>
-    <t>7018</t>
-  </si>
-  <si>
-    <t>Drop Group 7018</t>
-  </si>
-  <si>
-    <t>7019</t>
-  </si>
-  <si>
-    <t>Drop Group 7019</t>
-  </si>
-  <si>
-    <t>7020</t>
-  </si>
-  <si>
-    <t>Drop Group 7020</t>
-  </si>
-  <si>
-    <t>DropEntry</t>
-  </si>
-  <si>
-    <t>38e6bc608bd50c74</t>
-  </si>
-  <si>
-    <t>group_id</t>
-  </si>
-  <si>
-    <t>seq</t>
-  </si>
-  <si>
-    <t>item_id</t>
-  </si>
-  <si>
-    <t>count</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>ref&lt;DropGroup.id&gt;</t>
-  </si>
-  <si>
-    <t>ref&lt;Item.id&gt;</t>
   </si>
   <si>
     <t>server</t>
@@ -4600,7 +4624,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -4624,7 +4648,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
@@ -4638,10 +4662,10 @@
         <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>932</v>
+        <v>940</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>933</v>
+        <v>941</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4655,10 +4679,10 @@
         <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>932</v>
+        <v>940</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>933</v>
+        <v>941</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4672,7 +4696,7 @@
         <v>21</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>23</v>
@@ -4704,7 +4728,7 @@
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>31</v>
@@ -4721,142 +4745,142 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="5" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="5" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="5" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="5" t="s">
-        <v>948</v>
+        <v>956</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>949</v>
+        <v>957</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>951</v>
+        <v>959</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="5" t="s">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="5" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="5" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="5" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="5" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="5" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
     </row>
   </sheetData>
@@ -6382,10 +6406,10 @@
         <v>21</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>332</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6415,7 +6439,7 @@
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="42" customHeight="1">
@@ -6429,13 +6453,13 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>336</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>56</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>337</v>
@@ -6449,262 +6473,262 @@
         <v>339</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>62</v>
+        <v>340</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="5" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>68</v>
+        <v>344</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>76</v>
+        <v>348</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>88</v>
+        <v>356</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="5" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>94</v>
+        <v>360</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="5" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>42</v>
+        <v>364</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="5" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>56</v>
+        <v>336</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="5" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>62</v>
+        <v>340</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="5" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>68</v>
+        <v>344</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="5" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>76</v>
+        <v>348</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="5" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" s="5" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>88</v>
+        <v>356</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="5" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>94</v>
+        <v>360</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="5" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>42</v>
+        <v>364</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="5" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>56</v>
+        <v>336</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="5" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>62</v>
+        <v>340</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="26" spans="2:5">
       <c r="B26" s="5" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>68</v>
+        <v>344</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="5" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>76</v>
+        <v>348</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -6726,7 +6750,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -6750,7 +6774,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
@@ -6815,162 +6839,162 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="5" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="5" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="5" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="5" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="5" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="5" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="5" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="5" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="5" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="17" spans="2:3">
       <c r="B17" s="5" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="5" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="B19" s="5" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="5" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="B21" s="5" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="B22" s="5" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="B23" s="5" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="24" spans="2:3">
       <c r="B24" s="5" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="B25" s="5" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
     </row>
     <row r="26" spans="2:3">
       <c r="B26" s="5" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
     </row>
     <row r="27" spans="2:3">
       <c r="B27" s="5" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -6993,7 +7017,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -7015,7 +7039,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
@@ -7023,19 +7047,19 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -7043,19 +7067,19 @@
         <v>18</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -7063,19 +7087,19 @@
         <v>19</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>332</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -7095,7 +7119,7 @@
         <v>7</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -7106,7 +7130,7 @@
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="F6" s="5"/>
     </row>
@@ -7122,13 +7146,13 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="5" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>42</v>
@@ -7139,13 +7163,13 @@
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="5" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>62</v>
@@ -7156,13 +7180,13 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="5" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>76</v>
@@ -7173,13 +7197,13 @@
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="5" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>42</v>
@@ -7190,13 +7214,13 @@
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="5" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>62</v>
@@ -7207,13 +7231,13 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="5" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>76</v>
@@ -7224,13 +7248,13 @@
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="5" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>42</v>
@@ -7241,13 +7265,13 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="5" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>62</v>
@@ -7258,13 +7282,13 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="5" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>76</v>
@@ -7275,13 +7299,13 @@
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="5" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>42</v>
@@ -7292,13 +7316,13 @@
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="5" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>62</v>
@@ -7309,13 +7333,13 @@
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="5" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>76</v>
@@ -7326,13 +7350,13 @@
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="5" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>42</v>
@@ -7343,13 +7367,13 @@
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="5" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>62</v>
@@ -7360,13 +7384,13 @@
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="5" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>76</v>
@@ -7377,13 +7401,13 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="5" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>42</v>
@@ -7394,13 +7418,13 @@
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="5" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>62</v>
@@ -7411,13 +7435,13 @@
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="5" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>76</v>
@@ -7428,13 +7452,13 @@
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="5" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>42</v>
@@ -7445,13 +7469,13 @@
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="5" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>62</v>
@@ -7462,13 +7486,13 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="5" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>76</v>
@@ -7479,13 +7503,13 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="5" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>42</v>
@@ -7496,13 +7520,13 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="5" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>62</v>
@@ -7513,13 +7537,13 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="5" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>76</v>
@@ -7530,13 +7554,13 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="5" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>42</v>
@@ -7547,13 +7571,13 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="5" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>62</v>
@@ -7564,13 +7588,13 @@
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="5" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>76</v>
@@ -7581,13 +7605,13 @@
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="5" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>42</v>
@@ -7598,13 +7622,13 @@
     </row>
     <row r="36" spans="2:6">
       <c r="B36" s="5" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>62</v>
@@ -7615,13 +7639,13 @@
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="5" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>76</v>
@@ -7632,13 +7656,13 @@
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="5" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>42</v>
@@ -7649,13 +7673,13 @@
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="5" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>62</v>
@@ -7666,13 +7690,13 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="5" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>76</v>
@@ -7683,13 +7707,13 @@
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="5" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>42</v>
@@ -7700,13 +7724,13 @@
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="5" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>62</v>
@@ -7717,13 +7741,13 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="5" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>76</v>
@@ -7734,13 +7758,13 @@
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="5" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>42</v>
@@ -7751,13 +7775,13 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="5" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>62</v>
@@ -7768,13 +7792,13 @@
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="5" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>76</v>
@@ -7785,13 +7809,13 @@
     </row>
     <row r="47" spans="2:6">
       <c r="B47" s="5" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>42</v>
@@ -7802,13 +7826,13 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="5" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>62</v>
@@ -7819,13 +7843,13 @@
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="5" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>76</v>
@@ -7836,13 +7860,13 @@
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="5" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>42</v>
@@ -7853,13 +7877,13 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="5" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>62</v>
@@ -7870,13 +7894,13 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="5" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>76</v>
@@ -7887,13 +7911,13 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="5" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>42</v>
@@ -7904,13 +7928,13 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="5" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>62</v>
@@ -7921,13 +7945,13 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="5" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>76</v>
@@ -7938,13 +7962,13 @@
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="5" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="E56" s="5" t="s">
         <v>42</v>
@@ -7955,13 +7979,13 @@
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="5" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>62</v>
@@ -7972,13 +7996,13 @@
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="5" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>76</v>
@@ -7989,13 +8013,13 @@
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="5" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>42</v>
@@ -8006,13 +8030,13 @@
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="5" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>62</v>
@@ -8023,13 +8047,13 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="5" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>76</v>
@@ -8040,13 +8064,13 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="5" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="E62" s="5" t="s">
         <v>42</v>
@@ -8057,13 +8081,13 @@
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="5" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>62</v>
@@ -8074,13 +8098,13 @@
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="5" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="E64" s="5" t="s">
         <v>76</v>
@@ -8091,13 +8115,13 @@
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="5" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>42</v>
@@ -8108,13 +8132,13 @@
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="5" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>62</v>
@@ -8125,13 +8149,13 @@
     </row>
     <row r="67" spans="2:6">
       <c r="B67" s="5" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>76</v>
@@ -8168,7 +8192,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -8192,7 +8216,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
@@ -8206,13 +8230,13 @@
         <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>228</v>
@@ -8229,13 +8253,13 @@
         <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>228</v>
@@ -8258,7 +8282,7 @@
         <v>22</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>26</v>
@@ -8315,10 +8339,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="5" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>237</v>
@@ -8327,18 +8351,18 @@
         <v>47</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="5" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>42</v>
@@ -8347,18 +8371,18 @@
         <v>73</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="5" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>56</v>
@@ -8367,18 +8391,18 @@
         <v>53</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="5" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>62</v>
@@ -8387,18 +8411,18 @@
         <v>39</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="5" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>68</v>
@@ -8407,18 +8431,18 @@
         <v>47</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="5" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>76</v>
@@ -8427,18 +8451,18 @@
         <v>73</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="5" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>82</v>
@@ -8447,18 +8471,18 @@
         <v>53</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="5" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>88</v>
@@ -8467,18 +8491,18 @@
         <v>39</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="5" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>94</v>
@@ -8487,18 +8511,18 @@
         <v>47</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
     </row>
     <row r="17" spans="2:7">
       <c r="B17" s="5" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>100</v>
@@ -8507,18 +8531,18 @@
         <v>73</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
     </row>
     <row r="18" spans="2:7">
       <c r="B18" s="5" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>106</v>
@@ -8527,18 +8551,18 @@
         <v>53</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
     </row>
     <row r="19" spans="2:7">
       <c r="B19" s="5" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>112</v>
@@ -8547,18 +8571,18 @@
         <v>39</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
     </row>
     <row r="20" spans="2:7">
       <c r="B20" s="5" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>118</v>
@@ -8567,18 +8591,18 @@
         <v>47</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="21" spans="2:7">
       <c r="B21" s="5" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>124</v>
@@ -8587,18 +8611,18 @@
         <v>73</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="5" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>130</v>
@@ -8607,18 +8631,18 @@
         <v>53</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="5" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>136</v>
@@ -8627,18 +8651,18 @@
         <v>39</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="5" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>142</v>
@@ -8647,18 +8671,18 @@
         <v>47</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="5" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>148</v>
@@ -8667,18 +8691,18 @@
         <v>73</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
     </row>
     <row r="26" spans="2:7">
       <c r="B26" s="5" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>154</v>
@@ -8687,18 +8711,18 @@
         <v>53</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
     </row>
     <row r="27" spans="2:7">
       <c r="B27" s="5" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>160</v>
@@ -8707,18 +8731,18 @@
         <v>39</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
     </row>
     <row r="28" spans="2:7">
       <c r="B28" s="5" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>166</v>
@@ -8727,18 +8751,18 @@
         <v>47</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="5" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>172</v>
@@ -8747,18 +8771,18 @@
         <v>73</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="5" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>178</v>
@@ -8767,18 +8791,18 @@
         <v>53</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
     </row>
     <row r="31" spans="2:7">
       <c r="B31" s="5" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>184</v>
@@ -8787,18 +8811,18 @@
         <v>39</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
     </row>
     <row r="32" spans="2:7">
       <c r="B32" s="5" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>190</v>
@@ -8807,18 +8831,18 @@
         <v>47</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="5" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>196</v>
@@ -8827,18 +8851,18 @@
         <v>73</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
     </row>
     <row r="34" spans="2:7">
       <c r="B34" s="5" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>202</v>
@@ -8847,18 +8871,18 @@
         <v>53</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="5" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>208</v>
@@ -8867,18 +8891,18 @@
         <v>39</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="5" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>214</v>
@@ -8887,18 +8911,18 @@
         <v>47</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
     </row>
     <row r="37" spans="2:7">
       <c r="B37" s="5" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>220</v>
@@ -8907,207 +8931,207 @@
         <v>73</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
     </row>
     <row r="38" spans="2:7">
       <c r="B38" s="5" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>53</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
     </row>
     <row r="39" spans="2:7">
       <c r="B39" s="5" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>39</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
     </row>
     <row r="40" spans="2:7">
       <c r="B40" s="5" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
     </row>
     <row r="41" spans="2:7">
       <c r="B41" s="5" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
     </row>
     <row r="42" spans="2:7">
       <c r="B42" s="5" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>53</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
     </row>
     <row r="43" spans="2:7">
       <c r="B43" s="5" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>39</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
     </row>
     <row r="44" spans="2:7">
       <c r="B44" s="5" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
     </row>
     <row r="45" spans="2:7">
       <c r="B45" s="5" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
     </row>
     <row r="46" spans="2:7">
       <c r="B46" s="5" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>53</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
     </row>
     <row r="47" spans="2:7">
       <c r="B47" s="5" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>39</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>271</v>
@@ -9115,19 +9139,19 @@
     </row>
     <row r="48" spans="2:7">
       <c r="B48" s="5" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>275</v>
@@ -9135,19 +9159,19 @@
     </row>
     <row r="49" spans="2:7">
       <c r="B49" s="5" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>279</v>
@@ -9155,19 +9179,19 @@
     </row>
     <row r="50" spans="2:7">
       <c r="B50" s="5" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>53</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>283</v>
@@ -9175,19 +9199,19 @@
     </row>
     <row r="51" spans="2:7">
       <c r="B51" s="5" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>39</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>287</v>
@@ -9195,19 +9219,19 @@
     </row>
     <row r="52" spans="2:7">
       <c r="B52" s="5" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>291</v>
@@ -9215,690 +9239,690 @@
     </row>
     <row r="53" spans="2:7">
       <c r="B53" s="5" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
     </row>
     <row r="54" spans="2:7">
       <c r="B54" s="5" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>53</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
     </row>
     <row r="55" spans="2:7">
       <c r="B55" s="5" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>39</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
     </row>
     <row r="56" spans="2:7">
       <c r="B56" s="5" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="E56" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
     </row>
     <row r="57" spans="2:7">
       <c r="B57" s="5" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
     </row>
     <row r="58" spans="2:7">
       <c r="B58" s="5" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>53</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
     </row>
     <row r="59" spans="2:7">
       <c r="B59" s="5" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>39</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
     </row>
     <row r="60" spans="2:7">
       <c r="B60" s="5" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
     </row>
     <row r="61" spans="2:7">
       <c r="B61" s="5" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
     </row>
     <row r="62" spans="2:7">
       <c r="B62" s="5" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="E62" s="5" t="s">
         <v>53</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
     </row>
     <row r="63" spans="2:7">
       <c r="B63" s="5" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>39</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
     </row>
     <row r="64" spans="2:7">
       <c r="B64" s="5" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="E64" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
     </row>
     <row r="65" spans="2:7">
       <c r="B65" s="5" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
     </row>
     <row r="66" spans="2:7">
       <c r="B66" s="5" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>53</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
     </row>
     <row r="67" spans="2:7">
       <c r="B67" s="5" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>39</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
     </row>
     <row r="68" spans="2:7">
       <c r="B68" s="5" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="69" spans="2:7">
       <c r="B69" s="5" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="E69" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
     </row>
     <row r="70" spans="2:7">
       <c r="B70" s="5" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>53</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
     </row>
     <row r="71" spans="2:7">
       <c r="B71" s="5" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="E71" s="5" t="s">
         <v>39</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
     </row>
     <row r="72" spans="2:7">
       <c r="B72" s="5" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="73" spans="2:7">
       <c r="B73" s="5" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
     </row>
     <row r="74" spans="2:7">
       <c r="B74" s="5" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>53</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
     </row>
     <row r="75" spans="2:7">
       <c r="B75" s="5" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>39</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
     </row>
     <row r="76" spans="2:7">
       <c r="B76" s="5" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
     </row>
     <row r="77" spans="2:7">
       <c r="B77" s="5" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
     </row>
     <row r="78" spans="2:7">
       <c r="B78" s="5" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>53</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
     </row>
     <row r="79" spans="2:7">
       <c r="B79" s="5" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="E79" s="5" t="s">
         <v>39</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
     </row>
     <row r="80" spans="2:7">
       <c r="B80" s="5" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="E80" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="81" spans="2:7">
       <c r="B81" s="5" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="E81" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
     </row>
     <row r="82" spans="2:7">
       <c r="B82" s="5" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>53</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
     </row>
     <row r="83" spans="2:7">
       <c r="B83" s="5" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="E83" s="5" t="s">
         <v>39</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
     </row>
     <row r="84" spans="2:7">
       <c r="B84" s="5" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
     </row>
     <row r="85" spans="2:7">
       <c r="B85" s="5" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>73</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
     </row>
     <row r="86" spans="2:7">
       <c r="B86" s="5" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>53</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
     </row>
     <row r="87" spans="2:7">
       <c r="B87" s="5" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>327</v>
@@ -9907,10 +9931,10 @@
         <v>39</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -9941,7 +9965,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -9965,7 +9989,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
@@ -9979,13 +10003,13 @@
         <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -9999,13 +10023,13 @@
         <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -10019,13 +10043,13 @@
         <v>21</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -10057,11 +10081,11 @@
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="42" customHeight="1">
@@ -10073,687 +10097,687 @@
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="5" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="5" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>753</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="5" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="5" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="5" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="5" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="5" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="5" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="5" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="5" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="5" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="19" spans="2:6">
       <c r="B19" s="5" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="5" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="5" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="5" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="5" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="5" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="5" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="5" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="5" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="5" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="5" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="5" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="5" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="5" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="5" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="5" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="5" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="36" spans="2:6">
       <c r="B36" s="5" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="5" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="5" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="5" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="5" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="5" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="5" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="5" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="5" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="5" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="5" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
     <row r="47" spans="2:6">
       <c r="B47" s="5" t="s">
-        <v>903</v>
+        <v>911</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
     </row>
   </sheetData>
@@ -10776,7 +10800,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -10798,7 +10822,7 @@
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
@@ -10806,16 +10830,16 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -10823,16 +10847,16 @@
         <v>18</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -10840,13 +10864,13 @@
         <v>19</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>20</v>
@@ -10889,13 +10913,13 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="5" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>42</v>
@@ -10903,13 +10927,13 @@
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="5" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>68</v>
@@ -10917,13 +10941,13 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="5" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>42</v>
@@ -10931,13 +10955,13 @@
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="5" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>68</v>
@@ -10945,13 +10969,13 @@
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="5" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>42</v>
@@ -10959,13 +10983,13 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="5" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>68</v>
@@ -10973,13 +10997,13 @@
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="5" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>42</v>
@@ -10987,13 +11011,13 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="5" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>68</v>
@@ -11001,13 +11025,13 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="5" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>42</v>
@@ -11015,13 +11039,13 @@
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="5" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>68</v>
@@ -11029,13 +11053,13 @@
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="5" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>42</v>
@@ -11043,13 +11067,13 @@
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="5" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>68</v>
@@ -11057,13 +11081,13 @@
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="5" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>42</v>
@@ -11071,13 +11095,13 @@
     </row>
     <row r="21" spans="2:5">
       <c r="B21" s="5" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>68</v>
@@ -11085,13 +11109,13 @@
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="5" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>42</v>
@@ -11099,13 +11123,13 @@
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="5" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>68</v>
@@ -11113,13 +11137,13 @@
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="5" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>42</v>
@@ -11127,13 +11151,13 @@
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="5" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>68</v>
@@ -11141,13 +11165,13 @@
     </row>
     <row r="26" spans="2:5">
       <c r="B26" s="5" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>42</v>
@@ -11155,13 +11179,13 @@
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="5" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>68</v>
@@ -11169,13 +11193,13 @@
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="5" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>42</v>
@@ -11183,13 +11207,13 @@
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="5" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>68</v>
@@ -11197,13 +11221,13 @@
     </row>
     <row r="30" spans="2:5">
       <c r="B30" s="5" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>42</v>
@@ -11211,13 +11235,13 @@
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="5" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>68</v>
@@ -11225,13 +11249,13 @@
     </row>
     <row r="32" spans="2:5">
       <c r="B32" s="5" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>42</v>
@@ -11239,13 +11263,13 @@
     </row>
     <row r="33" spans="2:5">
       <c r="B33" s="5" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>68</v>
@@ -11253,13 +11277,13 @@
     </row>
     <row r="34" spans="2:5">
       <c r="B34" s="5" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>42</v>
@@ -11267,13 +11291,13 @@
     </row>
     <row r="35" spans="2:5">
       <c r="B35" s="5" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>68</v>
@@ -11281,13 +11305,13 @@
     </row>
     <row r="36" spans="2:5">
       <c r="B36" s="5" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>42</v>
@@ -11295,13 +11319,13 @@
     </row>
     <row r="37" spans="2:5">
       <c r="B37" s="5" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>68</v>
@@ -11309,13 +11333,13 @@
     </row>
     <row r="38" spans="2:5">
       <c r="B38" s="5" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>42</v>
@@ -11323,13 +11347,13 @@
     </row>
     <row r="39" spans="2:5">
       <c r="B39" s="5" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>68</v>
@@ -11337,13 +11361,13 @@
     </row>
     <row r="40" spans="2:5">
       <c r="B40" s="5" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>42</v>
@@ -11351,13 +11375,13 @@
     </row>
     <row r="41" spans="2:5">
       <c r="B41" s="5" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>68</v>
@@ -11365,13 +11389,13 @@
     </row>
     <row r="42" spans="2:5">
       <c r="B42" s="5" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>42</v>
@@ -11379,13 +11403,13 @@
     </row>
     <row r="43" spans="2:5">
       <c r="B43" s="5" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>68</v>
@@ -11393,13 +11417,13 @@
     </row>
     <row r="44" spans="2:5">
       <c r="B44" s="5" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>42</v>
@@ -11407,13 +11431,13 @@
     </row>
     <row r="45" spans="2:5">
       <c r="B45" s="5" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>68</v>
@@ -11421,13 +11445,13 @@
     </row>
     <row r="46" spans="2:5">
       <c r="B46" s="5" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>42</v>
@@ -11435,13 +11459,13 @@
     </row>
     <row r="47" spans="2:5">
       <c r="B47" s="5" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>68</v>
@@ -11449,13 +11473,13 @@
     </row>
     <row r="48" spans="2:5">
       <c r="B48" s="5" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>42</v>
@@ -11463,13 +11487,13 @@
     </row>
     <row r="49" spans="2:5">
       <c r="B49" s="5" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>68</v>
@@ -11477,13 +11501,13 @@
     </row>
     <row r="50" spans="2:5">
       <c r="B50" s="5" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>42</v>
@@ -11491,13 +11515,13 @@
     </row>
     <row r="51" spans="2:5">
       <c r="B51" s="5" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>68</v>
@@ -11505,13 +11529,13 @@
     </row>
     <row r="52" spans="2:5">
       <c r="B52" s="5" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>42</v>
@@ -11519,13 +11543,13 @@
     </row>
     <row r="53" spans="2:5">
       <c r="B53" s="5" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>68</v>
@@ -11533,13 +11557,13 @@
     </row>
     <row r="54" spans="2:5">
       <c r="B54" s="5" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>42</v>
@@ -11547,13 +11571,13 @@
     </row>
     <row r="55" spans="2:5">
       <c r="B55" s="5" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>68</v>
@@ -11561,13 +11585,13 @@
     </row>
     <row r="56" spans="2:5">
       <c r="B56" s="5" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="E56" s="5" t="s">
         <v>42</v>
@@ -11575,13 +11599,13 @@
     </row>
     <row r="57" spans="2:5">
       <c r="B57" s="5" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>68</v>
@@ -11589,13 +11613,13 @@
     </row>
     <row r="58" spans="2:5">
       <c r="B58" s="5" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="C58" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>42</v>
@@ -11603,13 +11627,13 @@
     </row>
     <row r="59" spans="2:5">
       <c r="B59" s="5" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>68</v>
@@ -11617,13 +11641,13 @@
     </row>
     <row r="60" spans="2:5">
       <c r="B60" s="5" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>42</v>
@@ -11631,13 +11655,13 @@
     </row>
     <row r="61" spans="2:5">
       <c r="B61" s="5" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="C61" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>68</v>
@@ -11645,13 +11669,13 @@
     </row>
     <row r="62" spans="2:5">
       <c r="B62" s="5" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="E62" s="5" t="s">
         <v>42</v>
@@ -11659,13 +11683,13 @@
     </row>
     <row r="63" spans="2:5">
       <c r="B63" s="5" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>68</v>
@@ -11673,13 +11697,13 @@
     </row>
     <row r="64" spans="2:5">
       <c r="B64" s="5" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
       <c r="E64" s="5" t="s">
         <v>42</v>
@@ -11687,13 +11711,13 @@
     </row>
     <row r="65" spans="2:5">
       <c r="B65" s="5" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>68</v>
@@ -11701,13 +11725,13 @@
     </row>
     <row r="66" spans="2:5">
       <c r="B66" s="5" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="C66" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>42</v>
@@ -11715,13 +11739,13 @@
     </row>
     <row r="67" spans="2:5">
       <c r="B67" s="5" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>68</v>
@@ -11729,13 +11753,13 @@
     </row>
     <row r="68" spans="2:5">
       <c r="B68" s="5" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>42</v>
@@ -11743,13 +11767,13 @@
     </row>
     <row r="69" spans="2:5">
       <c r="B69" s="5" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="C69" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="E69" s="5" t="s">
         <v>68</v>
@@ -11757,13 +11781,13 @@
     </row>
     <row r="70" spans="2:5">
       <c r="B70" s="5" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>42</v>
@@ -11771,13 +11795,13 @@
     </row>
     <row r="71" spans="2:5">
       <c r="B71" s="5" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
       <c r="E71" s="5" t="s">
         <v>68</v>
@@ -11785,13 +11809,13 @@
     </row>
     <row r="72" spans="2:5">
       <c r="B72" s="5" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>42</v>
@@ -11799,13 +11823,13 @@
     </row>
     <row r="73" spans="2:5">
       <c r="B73" s="5" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>68</v>
@@ -11813,13 +11837,13 @@
     </row>
     <row r="74" spans="2:5">
       <c r="B74" s="5" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>42</v>
@@ -11827,13 +11851,13 @@
     </row>
     <row r="75" spans="2:5">
       <c r="B75" s="5" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>68</v>
@@ -11841,13 +11865,13 @@
     </row>
     <row r="76" spans="2:5">
       <c r="B76" s="5" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>42</v>
@@ -11855,13 +11879,13 @@
     </row>
     <row r="77" spans="2:5">
       <c r="B77" s="5" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>68</v>
@@ -11869,13 +11893,13 @@
     </row>
     <row r="78" spans="2:5">
       <c r="B78" s="5" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>42</v>
@@ -11883,13 +11907,13 @@
     </row>
     <row r="79" spans="2:5">
       <c r="B79" s="5" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="E79" s="5" t="s">
         <v>68</v>
@@ -11897,13 +11921,13 @@
     </row>
     <row r="80" spans="2:5">
       <c r="B80" s="5" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="E80" s="5" t="s">
         <v>42</v>
@@ -11911,13 +11935,13 @@
     </row>
     <row r="81" spans="2:5">
       <c r="B81" s="5" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="E81" s="5" t="s">
         <v>68</v>
@@ -11925,13 +11949,13 @@
     </row>
     <row r="82" spans="2:5">
       <c r="B82" s="5" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>42</v>
@@ -11939,13 +11963,13 @@
     </row>
     <row r="83" spans="2:5">
       <c r="B83" s="5" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
       <c r="E83" s="5" t="s">
         <v>68</v>
@@ -11953,13 +11977,13 @@
     </row>
     <row r="84" spans="2:5">
       <c r="B84" s="5" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>42</v>
@@ -11967,13 +11991,13 @@
     </row>
     <row r="85" spans="2:5">
       <c r="B85" s="5" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>68</v>
@@ -11981,13 +12005,13 @@
     </row>
     <row r="86" spans="2:5">
       <c r="B86" s="5" t="s">
-        <v>903</v>
+        <v>911</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>327</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>42</v>
@@ -11995,13 +12019,13 @@
     </row>
     <row r="87" spans="2:5">
       <c r="B87" s="5" t="s">
-        <v>903</v>
+        <v>911</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>237</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="E87" s="5" t="s">
         <v>68</v>

--- a/examples/showcase/data/Battle.xlsx
+++ b/examples/showcase/data/Battle.xlsx
@@ -52,7 +52,7 @@
 Tuple cost, e.g. Gold,0,150
 Field: cost
 Type: struct&lt;ResourceCost&gt;
-Scope: all
+Groups: common
 Tuple fields: kind: enum&lt;ResourceKind&gt;, id: i32, count: i32
 Parser: tuple</t>
         </r>
@@ -81,7 +81,7 @@
 JSON object with element/power/radius
 Field: effect
 Type: struct&lt;SkillEffect&gt;
-Scope: all</t>
+Groups: common</t>
         </r>
       </text>
     </comment>
@@ -108,7 +108,7 @@
 Optional item requirement
 Field: required_item
 Type: optional&lt;ref&lt;Item.id&gt;&gt;
-Scope: all</t>
+Groups: common</t>
         </r>
       </text>
     </comment>
@@ -134,7 +134,7 @@
           <t xml:space="preserve">
 Field: cast_origin
 Type: struct&lt;Vec3&gt;
-Scope: all
+Groups: common
 Tuple fields: x: f32, y: f32, z: f32
 Parser: tuple</t>
         </r>
@@ -173,7 +173,7 @@
           <t xml:space="preserve">
 Field: spawn_pos
 Type: struct&lt;Vec3&gt;
-Scope: all
+Groups: common
 Tuple fields: x: f32, y: f32, z: f32
 Parser: tuple</t>
         </r>
@@ -212,7 +212,7 @@
           <t xml:space="preserve">
 Field: spawn_pos
 Type: struct&lt;Vec3&gt;
-Scope: all
+Groups: common
 Tuple fields: x: f32, y: f32, z: f32
 Parser: tuple</t>
         </r>
@@ -251,7 +251,7 @@
           <t xml:space="preserve">
 Field: entry_cost
 Type: struct&lt;ResourceCost&gt;
-Scope: all
+Groups: common
 Tuple fields: kind: enum&lt;ResourceKind&gt;, id: i32, count: i32
 Parser: tuple</t>
         </r>
@@ -282,16 +282,16 @@
     <t>id</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>70fc913f3e9b878f</t>
+    <t>c894d28c219e5edf</t>
   </si>
   <si>
     <t>#name</t>
@@ -345,7 +345,7 @@
     <t>struct&lt;Vec3&gt;(x: f32, y: f32, z: f32)</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
@@ -933,7 +933,7 @@
     <t>Character</t>
   </si>
   <si>
-    <t>34322ffa4454335d</t>
+    <t>2553615d93d56167</t>
   </si>
   <si>
     <t>rarity</t>
@@ -1230,7 +1230,7 @@
     <t>list</t>
   </si>
   <si>
-    <t>e92c79afa1e2e40b</t>
+    <t>e0e7445fb45c9c11</t>
   </si>
   <si>
     <t>character_id</t>
@@ -1251,7 +1251,7 @@
     <t>Buff</t>
   </si>
   <si>
-    <t>0b98849d3da9e5fb</t>
+    <t>a50d4c4ce4dfbd8f</t>
   </si>
   <si>
     <t>duration</t>
@@ -1473,7 +1473,7 @@
     <t>DropGroup</t>
   </si>
   <si>
-    <t>ddc8f184c6f4ca0b</t>
+    <t>6d78cabfe88d410d</t>
   </si>
   <si>
     <t>7001</t>
@@ -1599,7 +1599,7 @@
     <t>DropEntry</t>
   </si>
   <si>
-    <t>38e6bc608bd50c74</t>
+    <t>c220c766ac682968</t>
   </si>
   <si>
     <t>group_id</t>
@@ -1701,7 +1701,7 @@
     <t>Monster</t>
   </si>
   <si>
-    <t>3f0a6c4362bc5a57</t>
+    <t>a0b5c7b502b4ed6b</t>
   </si>
   <si>
     <t>level</t>
@@ -2502,7 +2502,7 @@
     <t>Stage</t>
   </si>
   <si>
-    <t>fd0a7a4819717e3b</t>
+    <t>9017b2a46b1a7899</t>
   </si>
   <si>
     <t>monster_ids</t>
@@ -3012,7 +3012,7 @@
     <t>StageReward</t>
   </si>
   <si>
-    <t>0c97ec70735264e3</t>
+    <t>6229c8bb1b11ec13</t>
   </si>
   <si>
     <t>stage_id</t>
@@ -3081,7 +3081,7 @@
     <t>Dungeon</t>
   </si>
   <si>
-    <t>d1401fb77a0a2d00</t>
+    <t>b940457777e98b6c</t>
   </si>
   <si>
     <t>stage_ids</t>
